--- a/stream_table.xlsx
+++ b/stream_table.xlsx
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5.932241463739437</v>
+        <v>8.805334848435308</v>
       </c>
       <c r="F3" t="n">
-        <v>1295.70746096677</v>
+        <v>1845.637371653705</v>
       </c>
     </row>
     <row r="4">
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.932241463739437</v>
+        <v>8.805334848435308</v>
       </c>
       <c r="F4" t="n">
-        <v>1295.70746096677</v>
+        <v>1845.637371653705</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.698039182285167</v>
+        <v>5.48906740929065</v>
       </c>
       <c r="F5" t="n">
-        <v>66.65015797140518</v>
+        <v>98.93005236327481</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.698039182285167</v>
+        <v>5.48906740929065</v>
       </c>
       <c r="F6" t="n">
-        <v>66.65015797140518</v>
+        <v>98.93005236327481</v>
       </c>
     </row>
     <row r="7">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.506199696982931</v>
+        <v>6.298444896496306</v>
       </c>
       <c r="F7" t="n">
-        <v>384.9467688143852</v>
+        <v>417.5313411172469</v>
       </c>
     </row>
     <row r="8">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5.124080949041672</v>
+        <v>7.995957361229651</v>
       </c>
       <c r="F8" t="n">
-        <v>977.4108501237899</v>
+        <v>1527.036082899733</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.142489582949865</v>
+        <v>7.999294779828134</v>
       </c>
       <c r="F9" t="n">
-        <v>982.313400688952</v>
+        <v>1527.924897546044</v>
       </c>
     </row>
     <row r="10">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2571244791474933</v>
+        <v>0.3999647389914068</v>
       </c>
       <c r="F10" t="n">
-        <v>49.11567003444761</v>
+        <v>76.39624487730219</v>
       </c>
     </row>
     <row r="11">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.885365103802371</v>
+        <v>7.599330040836727</v>
       </c>
       <c r="F11" t="n">
-        <v>933.1977306545044</v>
+        <v>1451.528652668741</v>
       </c>
     </row>
     <row r="12">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2572069754071907</v>
+        <v>0.4000268806279962</v>
       </c>
       <c r="F12" t="n">
-        <v>49.1326189705581</v>
+        <v>76.40922320067784</v>
       </c>
     </row>
     <row r="13">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.489736247663743</v>
+        <v>9.467712150892268</v>
       </c>
       <c r="F13" t="n">
-        <v>207.4702086300481</v>
+        <v>200.4286341162171</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5977910589810663</v>
+        <v>0.8914177864322125</v>
       </c>
       <c r="F14" t="n">
-        <v>12.89203903632143</v>
+        <v>20.98863404990027</v>
       </c>
     </row>
     <row r="15">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.017372556429157</v>
+        <v>9.006603133378098</v>
       </c>
       <c r="F15" t="n">
-        <v>182.8936314151229</v>
+        <v>179.8362127293603</v>
       </c>
     </row>
     <row r="16">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="F16" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
     <row r="17">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4547230530046102</v>
+        <v>0.4589859702730928</v>
       </c>
       <c r="F17" t="n">
-        <v>19.87855772279435</v>
+        <v>20.02701569170773</v>
       </c>
     </row>
     <row r="18">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5888555437147036</v>
+        <v>0.8811407060517076</v>
       </c>
       <c r="F18" t="n">
-        <v>12.59768812466117</v>
+        <v>20.62420100004125</v>
       </c>
     </row>
     <row r="19">
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01017961353132863</v>
+        <v>0.01211428654024057</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2882983448430565</v>
+        <v>0.3527251608331186</v>
       </c>
     </row>
     <row r="20">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="F20" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
     <row r="21">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="F21" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
     <row r="22">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4649026665359389</v>
+        <v>0.4711002568133334</v>
       </c>
       <c r="F22" t="n">
-        <v>20.1668560676374</v>
+        <v>20.37974085254085</v>
       </c>
     </row>
     <row r="23">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.177289364479152</v>
+        <v>1.357218062704981</v>
       </c>
       <c r="F23" t="n">
-        <v>324.7818437614179</v>
+        <v>328.2103549453821</v>
       </c>
     </row>
     <row r="24">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.177289364479152</v>
+        <v>1.357218062704981</v>
       </c>
       <c r="F24" t="n">
-        <v>324.7818437614179</v>
+        <v>328.2103549453821</v>
       </c>
     </row>
     <row r="25">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.328235264056651</v>
+        <v>4.940160668361585</v>
       </c>
       <c r="F25" t="n">
-        <v>59.98514217426467</v>
+        <v>89.03704712694733</v>
       </c>
     </row>
     <row r="26">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="F26" t="n">
-        <v>230.8977171302943</v>
+        <v>230.9784266575041</v>
       </c>
     </row>
     <row r="27">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="F27" t="n">
-        <v>230.8977171302943</v>
+        <v>230.9784266575041</v>
       </c>
     </row>
     <row r="28">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2691435545138166</v>
+        <v>0.2692376327459722</v>
       </c>
       <c r="F28" t="n">
-        <v>226.5916894016277</v>
+        <v>226.6708937712012</v>
       </c>
     </row>
     <row r="29">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.1345717772569083</v>
+        <v>0.1346188163729861</v>
       </c>
       <c r="F29" t="n">
-        <v>4.306027728666552</v>
+        <v>4.307532886302809</v>
       </c>
     </row>
     <row r="30">
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.388313945745524</v>
+        <v>2.568090084408374</v>
       </c>
       <c r="F30" t="n">
-        <v>93.87059576180603</v>
+        <v>97.12703564200582</v>
       </c>
     </row>
     <row r="31">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.388313945745524</v>
+        <v>2.568090084408374</v>
       </c>
       <c r="F31" t="n">
-        <v>93.87059576180603</v>
+        <v>97.12703564200582</v>
       </c>
     </row>
     <row r="32">
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.570568549995886</v>
+        <v>2.570568549995905</v>
       </c>
       <c r="F33" t="n">
-        <v>104.3582919498539</v>
+        <v>104.3582919498547</v>
       </c>
     </row>
     <row r="34">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.669566341355424</v>
+        <v>3.669566341355434</v>
       </c>
       <c r="F34" t="n">
-        <v>140.1870639088391</v>
+        <v>140.1870639088395</v>
       </c>
     </row>
     <row r="35">
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="F35" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
     <row r="36">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9.631989263638211</v>
+        <v>9.632016791071965</v>
       </c>
       <c r="F36" t="n">
-        <v>305.6496123754416</v>
+        <v>305.6501082821613</v>
       </c>
     </row>
     <row r="37">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.268202108648651</v>
+        <v>3.268202108648652</v>
       </c>
       <c r="F37" t="n">
-        <v>58.87666098730544</v>
+        <v>58.87666098730547</v>
       </c>
     </row>
     <row r="38">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3.391854372286896</v>
+        <v>3.391881899720625</v>
       </c>
       <c r="F38" t="n">
-        <v>61.10425651674843</v>
+        <v>61.10475242346707</v>
       </c>
     </row>
     <row r="39">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.181451876338113</v>
+        <v>7.979351009583292</v>
       </c>
       <c r="F41" t="n">
-        <v>174.0225940037081</v>
+        <v>206.543823621494</v>
       </c>
     </row>
     <row r="42">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6.181451876338113</v>
+        <v>7.979351009583292</v>
       </c>
       <c r="F42" t="n">
-        <v>174.0225940037081</v>
+        <v>206.543823621494</v>
       </c>
     </row>
     <row r="43">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4.162875217484488</v>
+        <v>5.960068763988501</v>
       </c>
       <c r="F43" t="n">
-        <v>86.81281546525963</v>
+        <v>119.3035611957149</v>
       </c>
     </row>
     <row r="44">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.018576658853624</v>
+        <v>2.019282245594792</v>
       </c>
       <c r="F44" t="n">
-        <v>87.20977853844848</v>
+        <v>87.24026242577914</v>
       </c>
     </row>
     <row r="45">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12.17459970892824</v>
+        <v>12.17645308772521</v>
       </c>
       <c r="F45" t="n">
-        <v>322.752802594084</v>
+        <v>322.8109175575095</v>
       </c>
     </row>
     <row r="46">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>16.33747492641273</v>
+        <v>18.13652185171371</v>
       </c>
       <c r="F46" t="n">
-        <v>409.5656180593436</v>
+        <v>442.1144787532244</v>
       </c>
     </row>
     <row r="47">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16.33747492641273</v>
+        <v>18.13652185171371</v>
       </c>
       <c r="F47" t="n">
-        <v>409.5656180593436</v>
+        <v>442.1144787532244</v>
       </c>
     </row>
     <row r="48">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>10.62872950253066</v>
+        <v>12.42088951864316</v>
       </c>
       <c r="F48" t="n">
-        <v>191.4765619880898</v>
+        <v>223.7623246783565</v>
       </c>
     </row>
     <row r="49">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.708745423882072</v>
+        <v>5.715632333070551</v>
       </c>
       <c r="F49" t="n">
-        <v>218.0890560712539</v>
+        <v>218.3521540748678</v>
       </c>
     </row>
     <row r="50">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.02532988163151</v>
+        <v>11.02690850495147</v>
       </c>
       <c r="F50" t="n">
-        <v>198.6213178175917</v>
+        <v>198.6497567167007</v>
       </c>
     </row>
     <row r="51">
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4.927918194993625</v>
+        <v>4.928623781734792</v>
       </c>
       <c r="F53" t="n">
-        <v>178.7191031108034</v>
+        <v>178.7495869981341</v>
       </c>
     </row>
     <row r="54">
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.927918194993625</v>
+        <v>4.928623781734792</v>
       </c>
       <c r="F54" t="n">
-        <v>178.7191031108034</v>
+        <v>178.7495869981341</v>
       </c>
     </row>
     <row r="55">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.860323934146457</v>
+        <v>1.860347289067589</v>
       </c>
       <c r="F55" t="n">
-        <v>54.58761833431112</v>
+        <v>54.58842615732538</v>
       </c>
     </row>
     <row r="56">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.860323934146457</v>
+        <v>1.860347289067589</v>
       </c>
       <c r="F56" t="n">
-        <v>54.58761833431112</v>
+        <v>54.58842615732538</v>
       </c>
     </row>
     <row r="57">
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.09978954609402255</v>
+        <v>0.09981176121597812</v>
       </c>
       <c r="F57" t="n">
-        <v>1.699515759527298</v>
+        <v>1.699894105269323</v>
       </c>
     </row>
     <row r="58">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.09978954609402255</v>
+        <v>0.09981176121597812</v>
       </c>
       <c r="F58" t="n">
-        <v>1.699515759527298</v>
+        <v>1.699894105269323</v>
       </c>
     </row>
     <row r="59">
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.990849965748224</v>
+        <v>1.990903011398164</v>
       </c>
       <c r="F59" t="n">
-        <v>56.28713409383841</v>
+        <v>56.2883202625947</v>
       </c>
     </row>
     <row r="60">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.990849965748224</v>
+        <v>1.990903011398164</v>
       </c>
       <c r="F60" t="n">
-        <v>56.28713409383841</v>
+        <v>56.2883202625947</v>
       </c>
     </row>
     <row r="61">
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.1301602775139424</v>
+        <v>0.1301892537599715</v>
       </c>
       <c r="F61" t="n">
-        <v>2.344837399413673</v>
+        <v>2.345359406485886</v>
       </c>
     </row>
     <row r="62">
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1236522636382453</v>
+        <v>0.1236797910719729</v>
       </c>
       <c r="F62" t="n">
-        <v>2.227595529442989</v>
+        <v>2.228091436161592</v>
       </c>
     </row>
     <row r="63">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.860689688234281</v>
+        <v>1.860713757638193</v>
       </c>
       <c r="F63" t="n">
-        <v>53.94229669442474</v>
+        <v>53.94296085610881</v>
       </c>
     </row>
     <row r="64">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>12.59686918934608</v>
+        <v>12.59703213921056</v>
       </c>
       <c r="F64" t="n">
-        <v>226.9325984460697</v>
+        <v>226.9355339878783</v>
       </c>
     </row>
     <row r="65">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>12.59686918934608</v>
+        <v>12.59703213921056</v>
       </c>
       <c r="F65" t="n">
-        <v>226.9325984460697</v>
+        <v>226.9355339878783</v>
       </c>
     </row>
     <row r="66">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12.60975505681996</v>
+        <v>12.6099208753328</v>
       </c>
       <c r="F66" t="n">
-        <v>227.1520576550174</v>
+        <v>227.1550420527761</v>
       </c>
     </row>
     <row r="67">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.847803820760401</v>
+        <v>1.847825021515956</v>
       </c>
       <c r="F67" t="n">
-        <v>53.72283748547709</v>
+        <v>53.723452791211</v>
       </c>
     </row>
     <row r="68">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1.847803820760401</v>
+        <v>1.847825021515956</v>
       </c>
       <c r="F68" t="n">
-        <v>53.72283748547709</v>
+        <v>53.723452791211</v>
       </c>
     </row>
     <row r="69">
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10.28355737225821</v>
+        <v>10.28358489969196</v>
       </c>
       <c r="F70" t="n">
-        <v>522.6517384058458</v>
+        <v>522.6522343125655</v>
       </c>
     </row>
     <row r="71">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10.28355737225821</v>
+        <v>10.28358489969196</v>
       </c>
       <c r="F71" t="n">
-        <v>522.6517384058458</v>
+        <v>522.6522343125655</v>
       </c>
     </row>
     <row r="72">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1.847261911140401</v>
+        <v>1.847283111895956</v>
       </c>
       <c r="F72" t="n">
-        <v>53.58302480351708</v>
+        <v>53.58364010925099</v>
       </c>
     </row>
     <row r="73">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="F78" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
     <row r="79">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="F79" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
     <row r="80">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>9.472095609433767</v>
+        <v>9.46558910365119</v>
       </c>
       <c r="F80" t="n">
-        <v>202.7721891379172</v>
+        <v>199.863228421068</v>
       </c>
     </row>
     <row r="81">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.01764063822997675</v>
+        <v>0.002123047241076949</v>
       </c>
       <c r="F81" t="n">
-        <v>4.698019492130949</v>
+        <v>0.565405695149131</v>
       </c>
     </row>
     <row r="82">
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="F82" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
     <row r="83">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="F83" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
     <row r="84">
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.5976981317499798</v>
+        <v>0.891269580504547</v>
       </c>
       <c r="F84" t="n">
-        <v>12.86729084199293</v>
+        <v>20.94916414365624</v>
       </c>
     </row>
     <row r="85">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>9.292723108654603e-05</v>
+        <v>0.0001482059276655101</v>
       </c>
       <c r="F85" t="n">
-        <v>0.02474819432850677</v>
+        <v>0.03946990624402331</v>
       </c>
     </row>
     <row r="86">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4.505524628535802</v>
+        <v>6.297378731066566</v>
       </c>
       <c r="F86" t="n">
-        <v>384.7669859356826</v>
+        <v>417.2474020723294</v>
       </c>
     </row>
     <row r="87">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.505524628535802</v>
+        <v>6.297378731066566</v>
       </c>
       <c r="F87" t="n">
-        <v>384.7669859356826</v>
+        <v>417.2474020723294</v>
       </c>
     </row>
     <row r="88">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0006750684471292648</v>
+        <v>0.001066165429740137</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1797828787025716</v>
+        <v>0.283939044917534</v>
       </c>
     </row>
     <row r="89">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.039179082526648</v>
+        <v>2.046065991715117</v>
       </c>
       <c r="F89" t="n">
-        <v>77.90199216241473</v>
+        <v>78.16509016602832</v>
       </c>
     </row>
     <row r="90">
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>10.28355737225821</v>
+        <v>10.28358489969196</v>
       </c>
       <c r="F90" t="n">
-        <v>522.6517384058458</v>
+        <v>522.6522343125655</v>
       </c>
     </row>
     <row r="91">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.006508013875697122</v>
+        <v>0.006509462687998574</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1172418699706837</v>
+        <v>0.1172679703242943</v>
       </c>
     </row>
     <row r="92">
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.01840863390819256</v>
+        <v>0.003337418598482597</v>
       </c>
       <c r="F92" t="n">
-        <v>4.902550565162027</v>
+        <v>0.8888146463106883</v>
       </c>
     </row>
     <row r="93">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5.142489582949865</v>
+        <v>7.999294779828134</v>
       </c>
       <c r="F93" t="n">
-        <v>982.313400688952</v>
+        <v>1527.924897546044</v>
       </c>
     </row>
     <row r="94">
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5.142572077878717</v>
+        <v>7.999356919261684</v>
       </c>
       <c r="F95" t="n">
-        <v>982.3303493708534</v>
+        <v>1527.937875448637</v>
       </c>
     </row>
     <row r="96">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5.936393202473185</v>
+        <v>8.815229668061383</v>
       </c>
       <c r="F96" t="n">
-        <v>1297.511879146651</v>
+        <v>1850.161475644985</v>
       </c>
     </row>
     <row r="97">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.5936393202473185</v>
+        <v>0.8815229668061383</v>
       </c>
       <c r="F97" t="n">
-        <v>11.08762085644052</v>
+        <v>16.46453005862058</v>
       </c>
     </row>
   </sheetData>
@@ -3197,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.088368575711486</v>
+        <v>1.718400825526719</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.035555691031838</v>
+        <v>6.277508476626917</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.8082389024438938</v>
+        <v>0.8085214196575742</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.907695913285422e-24</v>
+        <v>7.0961411384608e-24</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>7.829455221823569e-05</v>
+        <v>0.0009041266240976428</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.088368575711486</v>
+        <v>1.718400825526719</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.035555691031838</v>
+        <v>6.277508476626917</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3345,10 +3345,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.8082389024438938</v>
+        <v>0.8085214196575742</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.907695913285422e-24</v>
+        <v>7.0961411384608e-24</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.829455221823569e-05</v>
+        <v>0.0009041266240976428</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -3442,13 +3442,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0006663133661775077</v>
+        <v>0.000989021154827144</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.69737286891899</v>
+        <v>5.488078388135823</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0006663133661775077</v>
+        <v>0.000989021154827144</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.69737286891899</v>
+        <v>5.488078388135823</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0006663133661775077</v>
+        <v>0.000989021154827144</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.69737286891899</v>
+        <v>5.488078388135823</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000678466927273913</v>
+        <v>0.001071216271709918</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.138422904040175e-05</v>
+        <v>0.0005933726960295194</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.087690108784212</v>
+        <v>1.717329609255009</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.035555691031838</v>
+        <v>6.277508476626917</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3877,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0008082389024439394</v>
+        <v>0.0008085214196576189</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.907695913285422e-24</v>
+        <v>7.0961411384608e-24</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.691032317783394e-05</v>
+        <v>0.0003107539280681235</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -3995,10 +3995,10 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.106098742692405</v>
+        <v>1.720667027853492</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.035555691031838</v>
+        <v>6.277508476626917</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -4010,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0008082389024439394</v>
+        <v>0.0008085214196576189</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.907695913285422e-24</v>
+        <v>7.0961411384608e-24</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -4040,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.691032317783394e-05</v>
+        <v>0.0003107539280681235</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -4128,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05530493713462024</v>
+        <v>0.0860333513926746</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2017777845515919</v>
+        <v>0.3138754238313459</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -4143,10 +4143,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>4.041194512219697e-05</v>
+        <v>4.042607098288095e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.53847956642711e-26</v>
+        <v>3.5480705692304e-25</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.345516158891697e-06</v>
+        <v>1.553769640340617e-05</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -4261,10 +4261,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.050793805557784</v>
+        <v>1.634633676460817</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.833777906480246</v>
+        <v>5.96363305279557</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -4276,10 +4276,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0007678269573217424</v>
+        <v>0.0007680953486747378</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.812311117621151e-24</v>
+        <v>6.741334081537759e-24</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.556480701894224e-05</v>
+        <v>0.0002952162316647173</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -4394,10 +4394,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.05542918981117786</v>
+        <v>0.08615145506787986</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2017777855960128</v>
+        <v>0.3138754255601163</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4506,13 +4506,13 @@
         <v>0.006234</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4649769364799838</v>
+        <v>0.4649769364799967</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>8.963894338398227</v>
+        <v>8.963921865831969</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01774557162889456</v>
+        <v>0.00221244825986644</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -4542,13 +4542,13 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.001118236103612132</v>
+        <v>0.0008352792180895346</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.005749014481195774</v>
+        <v>0.000555375617156357</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0003155203245473572</v>
+        <v>3.625126069399194e-05</v>
       </c>
       <c r="AH13" t="n">
         <v>0.000321834</v>
@@ -4572,7 +4572,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.003067610867282763</v>
+        <v>0.002304974844496024</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -4639,13 +4639,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005348101984210076</v>
+        <v>0.007941648349604849</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5856171672710033</v>
+        <v>0.869610494281731</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4660,13 +4660,13 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0001088477423452083</v>
+        <v>0.0001718572682793962</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.002674050992105038</v>
+        <v>0.003970824174802425</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4675,13 +4675,13 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.002025661409633783</v>
+        <v>0.002026369472825973</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.001909605518804226</v>
+        <v>0.007103244382843643</v>
       </c>
       <c r="AG14" t="n">
-        <v>8.805067545264276e-05</v>
+        <v>0.000367319739306008</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.957338751199181e-05</v>
+        <v>0.0002260287628192135</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -4766,19 +4766,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.105938000000002e-05</v>
+        <v>1.105938e-05</v>
       </c>
       <c r="R15" t="n">
         <v>0.006234000000000003</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2052546900431927</v>
+        <v>0.2036621057748839</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>8.768893531830408</v>
+        <v>8.766250726263989</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0001049333989178137</v>
+        <v>8.940101878949082e-05</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -4808,13 +4808,13 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.001118236103612131</v>
+        <v>0.0008352792180895338</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.005749014481195774</v>
+        <v>0.0005553756171563567</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0003155203245473574</v>
+        <v>3.625126069399195e-05</v>
       </c>
       <c r="AH15" t="n">
         <v>0.000321834</v>
@@ -4826,7 +4826,7 @@
         <v>0.002529914000000001</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0003664160000000001</v>
+        <v>0.0003664159999999996</v>
       </c>
       <c r="AL15" t="n">
         <v>0.0002124779999999999</v>
@@ -4838,7 +4838,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.003067610867282765</v>
+        <v>0.002304974844496023</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -4905,13 +4905,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.936402999999984</v>
+        <v>2.936402999999997</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>6.695586263638226</v>
+        <v>6.695613791071969</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -5038,13 +5038,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2597222464367912</v>
+        <v>0.2613148307051129</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.195000806567819</v>
+        <v>0.19767113956798</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.003016555279403728</v>
+        <v>0.004952864901581989</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.577769100444481</v>
+        <v>0.8604849911895133</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -5192,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.592051125866229e-05</v>
+        <v>2.365134061388612e-05</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -5201,19 +5201,19 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.002674050992105038</v>
+        <v>0.003970824174802425</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.001337025496052519</v>
+        <v>0.001985412087401212</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.002025661409633783</v>
+        <v>0.002026369472825973</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.001909605518804226</v>
+        <v>0.007103244382843643</v>
       </c>
       <c r="AG18" t="n">
-        <v>8.805067545264276e-05</v>
+        <v>0.000367319739306008</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.957338751199181e-05</v>
+        <v>0.0002260287628192135</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -5304,13 +5304,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.002331546704806348</v>
+        <v>0.00298878344802286</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.007848066826522282</v>
+        <v>0.009125503092217713</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5437,13 +5437,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2620537931415975</v>
+        <v>0.2643036141531357</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2028488733943413</v>
+        <v>0.2067966426601977</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5570,13 +5570,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2620537931415975</v>
+        <v>0.2643036141531357</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2028488733943413</v>
+        <v>0.2067966426601977</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5703,13 +5703,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2620537931415975</v>
+        <v>0.2643036141531357</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2028488733943413</v>
+        <v>0.2067966426601977</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5836,13 +5836,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>6.663133661775076e-05</v>
+        <v>9.890211548271438e-05</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3697372868918989</v>
+        <v>0.5488078388135822</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5857,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.398480144648209e-06</v>
+        <v>5.050841969780978e-06</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -5872,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>5.138422904040175e-05</v>
+        <v>0.0005933726960295194</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -5969,13 +5969,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>6.663133661775076e-05</v>
+        <v>9.890211548271438e-05</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3697372868918989</v>
+        <v>0.5488078388135822</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.398480144648209e-06</v>
+        <v>5.050841969780978e-06</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -6035,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>5.138422904040175e-05</v>
+        <v>0.0005933726960295194</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -6102,13 +6102,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0005996820295597569</v>
+        <v>0.0008901190393444296</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.327635582027091</v>
+        <v>4.939270549322241</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -6304,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="AQ26" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="AQ27" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.2691435545138166</v>
+        <v>0.2692376327459722</v>
       </c>
     </row>
     <row r="29">
@@ -6652,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1345717772569083</v>
+        <v>0.1346188163729861</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -6770,10 +6770,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.6148613270829</v>
+        <v>1.615425796475833</v>
       </c>
       <c r="U30" t="n">
-        <v>0.3697372868918989</v>
+        <v>0.5488078388135822</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.4037153317707249</v>
+        <v>0.4038564491189583</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6903,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.6148613270829</v>
+        <v>1.615425796475833</v>
       </c>
       <c r="U31" t="n">
-        <v>0.3697372868918989</v>
+        <v>0.5488078388135822</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6918,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4037153317707249</v>
+        <v>0.4038564491189583</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -7166,13 +7166,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.290074883251729</v>
+        <v>1.290074883251738</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.280493666744158</v>
+        <v>1.280493666744167</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -7299,13 +7299,13 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.646328116748254</v>
+        <v>1.646328116748258</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.023238224607171</v>
+        <v>2.023238224607176</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7432,13 +7432,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.936402999999984</v>
+        <v>2.936402999999997</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>6.695586263638226</v>
+        <v>6.695613791071969</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7565,13 +7565,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.936402999999984</v>
+        <v>2.936402999999997</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>6.695586263638226</v>
+        <v>6.695613791071969</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.268202108648651</v>
+        <v>3.268202108648652</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7837,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.391854372286896</v>
+        <v>3.391881899720625</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.2626534751711573</v>
+        <v>0.2651937331924801</v>
       </c>
       <c r="T41" t="n">
-        <v>1.6148613270829</v>
+        <v>1.615425796475833</v>
       </c>
       <c r="U41" t="n">
-        <v>3.900221742313331</v>
+        <v>5.694875030796021</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8248,7 +8248,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.4037153317707249</v>
+        <v>0.4038564491189583</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -8363,13 +8363,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.2626534751711573</v>
+        <v>0.2651937331924801</v>
       </c>
       <c r="T42" t="n">
-        <v>1.6148613270829</v>
+        <v>1.615425796475833</v>
       </c>
       <c r="U42" t="n">
-        <v>3.900221742313331</v>
+        <v>5.694875030796021</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8381,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.4037153317707249</v>
+        <v>0.4038564491189583</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -8496,13 +8496,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.2626534751711573</v>
+        <v>0.2651937331924801</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.900221742313331</v>
+        <v>5.694875030796021</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.6148613270829</v>
+        <v>1.615425796475833</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.4037153317707249</v>
+        <v>0.4038564491189583</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -8762,13 +8762,13 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.298539654593457</v>
+        <v>2.299089165547477</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>9.876060054334783</v>
+        <v>9.877363922177731</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -8895,13 +8895,13 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.561193129764614</v>
+        <v>2.564282898739958</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>13.77628179664811</v>
+        <v>15.57223895297375</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -9028,13 +9028,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.561193129764614</v>
+        <v>2.564282898739958</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>13.77628179664811</v>
+        <v>15.57223895297375</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -9167,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>10.62872950253066</v>
+        <v>12.42088951864316</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -9294,13 +9294,13 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.561193129764614</v>
+        <v>2.564282898739958</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>3.147552294117458</v>
+        <v>3.151349434330593</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>11.02532988163151</v>
+        <v>11.02690850495147</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>1.9289901710937</v>
+        <v>1.929554640486633</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
         <v>1.68713681538</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.8521947383907249</v>
+        <v>0.8523358557389582</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -9962,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1.9289901710937</v>
+        <v>1.929554640486633</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1.68713681538</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.8521947383907249</v>
+        <v>0.8523358557389582</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.01928990171093692</v>
+        <v>0.0192955464048663</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -10104,13 +10104,13 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.05396874429850618</v>
+        <v>0.05397805804348943</v>
       </c>
       <c r="X55" t="n">
         <v>1.68713681538</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.08314013213701388</v>
+        <v>0.08314852861923372</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -10228,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.01928990171093692</v>
+        <v>0.0192955464048663</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -10237,13 +10237,13 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.05396874429850618</v>
+        <v>0.05397805804348943</v>
       </c>
       <c r="X56" t="n">
         <v>1.68713681538</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.08314013213701388</v>
+        <v>0.08314852861923372</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>0.09978954609402255</v>
+        <v>0.09981176121597812</v>
       </c>
       <c r="W57" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0.09978954609402255</v>
+        <v>0.09981176121597812</v>
       </c>
       <c r="W58" t="n">
         <v>0</v>
@@ -10627,22 +10627,22 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.001203689866762465</v>
+        <v>0.001204042095663656</v>
       </c>
       <c r="U59" t="n">
-        <v>0.1301602775139424</v>
+        <v>0.1301892537599715</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01301602775139424</v>
+        <v>0.01301892537599714</v>
       </c>
       <c r="W59" t="n">
-        <v>0.003367649644226783</v>
+        <v>0.003368230821913738</v>
       </c>
       <c r="X59" t="n">
-        <v>1.764867227800541</v>
+        <v>1.76488389906538</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.0614467525513568</v>
+        <v>0.06145031965923847</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -10760,22 +10760,22 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.001203689866762465</v>
+        <v>0.001204042095663656</v>
       </c>
       <c r="U60" t="n">
-        <v>0.1301602775139424</v>
+        <v>0.1301892537599715</v>
       </c>
       <c r="V60" t="n">
-        <v>0.01301602775139424</v>
+        <v>0.01301892537599714</v>
       </c>
       <c r="W60" t="n">
-        <v>0.003367649644226783</v>
+        <v>0.003368230821913738</v>
       </c>
       <c r="X60" t="n">
-        <v>1.764867227800541</v>
+        <v>1.76488389906538</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.0614467525513568</v>
+        <v>0.06145031965923847</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>0.1301602775139424</v>
+        <v>0.1301892537599715</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -11029,7 +11029,7 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0.1236522636382453</v>
+        <v>0.1236797910719729</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -11159,22 +11159,22 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.001203689866762465</v>
+        <v>0.001204042095663656</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.01301602775139424</v>
+        <v>0.01301892537599714</v>
       </c>
       <c r="W63" t="n">
-        <v>0.003367649644226783</v>
+        <v>0.003368230821913738</v>
       </c>
       <c r="X63" t="n">
-        <v>1.764867227800541</v>
+        <v>1.76488389906538</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.0614467525513568</v>
+        <v>0.06145031965923847</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -11295,7 +11295,7 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>12.59686918934608</v>
+        <v>12.59703213921056</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>12.59686918934608</v>
+        <v>12.59703213921056</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -11561,10 +11561,10 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>12.59686918934608</v>
+        <v>12.59703213921056</v>
       </c>
       <c r="V66" t="n">
-        <v>0.01288586747388029</v>
+        <v>0.01288873612223717</v>
       </c>
       <c r="W66" t="n">
         <v>0</v>
@@ -11691,22 +11691,22 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.001203689866762465</v>
+        <v>0.001204042095663656</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0001301602775139431</v>
+        <v>0.0001301892537599707</v>
       </c>
       <c r="W67" t="n">
-        <v>0.003367649644226783</v>
+        <v>0.003368230821913738</v>
       </c>
       <c r="X67" t="n">
-        <v>1.764867227800541</v>
+        <v>1.76488389906538</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.0614467525513568</v>
+        <v>0.06145031965923847</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -11824,22 +11824,22 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.001203689866762465</v>
+        <v>0.001204042095663656</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0.0001301602775139431</v>
+        <v>0.0001301892537599707</v>
       </c>
       <c r="W68" t="n">
-        <v>0.003367649644226783</v>
+        <v>0.003368230821913738</v>
       </c>
       <c r="X68" t="n">
-        <v>1.764867227800541</v>
+        <v>1.76488389906538</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.0614467525513568</v>
+        <v>0.06145031965923847</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -12087,13 +12087,13 @@
         <v>0.006234</v>
       </c>
       <c r="S70" t="n">
-        <v>0.4649769364799838</v>
+        <v>0.4649769364799967</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>8.963894338398227</v>
+        <v>8.963921865831969</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -12220,13 +12220,13 @@
         <v>0.006234</v>
       </c>
       <c r="S71" t="n">
-        <v>0.4649769364799838</v>
+        <v>0.4649769364799967</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>8.963894338398227</v>
+        <v>8.963921865831969</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -12356,22 +12356,22 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0.001203689866762465</v>
+        <v>0.001204042095663656</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>0.0001301602775139431</v>
+        <v>0.0001301892537599707</v>
       </c>
       <c r="W72" t="n">
-        <v>0.003367649644226783</v>
+        <v>0.003368230821913738</v>
       </c>
       <c r="X72" t="n">
-        <v>1.764867227800541</v>
+        <v>1.76488389906538</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.0614467525513568</v>
+        <v>0.06145031965923847</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -13151,13 +13151,13 @@
         <v>0.006234</v>
       </c>
       <c r="S78" t="n">
-        <v>0.4649769364799838</v>
+        <v>0.4649769364799967</v>
       </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>8.963894338398227</v>
+        <v>8.963921865831969</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>0.0001049333989178138</v>
+        <v>8.94010187894908e-05</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -13187,13 +13187,13 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.001118236103612132</v>
+        <v>0.0008352792180895346</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.005749014481195774</v>
+        <v>0.000555375617156357</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.0003155203245473572</v>
+        <v>3.625126069399194e-05</v>
       </c>
       <c r="AH78" t="n">
         <v>0.000321834</v>
@@ -13217,7 +13217,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO78" t="n">
-        <v>0.003067610867282763</v>
+        <v>0.002304974844496024</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -13284,13 +13284,13 @@
         <v>0.006234</v>
       </c>
       <c r="S79" t="n">
-        <v>0.4649769364799838</v>
+        <v>0.4649769364799967</v>
       </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>8.963894338398227</v>
+        <v>8.963921865831969</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -13305,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>0.0001049333989178138</v>
+        <v>8.94010187894908e-05</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -13320,13 +13320,13 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0.001118236103612132</v>
+        <v>0.0008352792180895346</v>
       </c>
       <c r="AF79" t="n">
-        <v>0.005749014481195774</v>
+        <v>0.000555375617156357</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.0003155203245473572</v>
+        <v>3.625126069399194e-05</v>
       </c>
       <c r="AH79" t="n">
         <v>0.000321834</v>
@@ -13350,7 +13350,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO79" t="n">
-        <v>0.003067610867282763</v>
+        <v>0.002304974844496024</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -13417,13 +13417,13 @@
         <v>0.006234</v>
       </c>
       <c r="S80" t="n">
-        <v>0.4649769364799838</v>
+        <v>0.4649769364799967</v>
       </c>
       <c r="T80" t="n">
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>8.963894338398227</v>
+        <v>8.963921865831969</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -13438,7 +13438,7 @@
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.0001049333989178138</v>
+        <v>8.94010187894908e-05</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -13453,13 +13453,13 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0.001118236103612132</v>
+        <v>0.0008352792180895346</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.005749014481195774</v>
+        <v>0.000555375617156357</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.0003155203245473572</v>
+        <v>3.625126069399194e-05</v>
       </c>
       <c r="AH80" t="n">
         <v>0.000321834</v>
@@ -13483,7 +13483,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO80" t="n">
-        <v>0.003067610867282763</v>
+        <v>0.002304974844496024</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -13571,7 +13571,7 @@
         <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>0.01764063822997675</v>
+        <v>0.002123047241076949</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -13683,13 +13683,13 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.005348101984210076</v>
+        <v>0.007941648349604849</v>
       </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>0.5856171672710033</v>
+        <v>0.869610494281731</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -13704,13 +13704,13 @@
         <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.592051125866229e-05</v>
+        <v>2.365134061388612e-05</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.002674050992105038</v>
+        <v>0.003970824174802425</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -13719,13 +13719,13 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.002025661409633783</v>
+        <v>0.002026369472825973</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.001909605518804226</v>
+        <v>0.007103244382843643</v>
       </c>
       <c r="AG82" t="n">
-        <v>8.805067545264276e-05</v>
+        <v>0.000367319739306008</v>
       </c>
       <c r="AH82" t="n">
         <v>0</v>
@@ -13749,7 +13749,7 @@
         <v>0</v>
       </c>
       <c r="AO82" t="n">
-        <v>1.957338751199181e-05</v>
+        <v>0.0002260287628192135</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -13816,13 +13816,13 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.005348101984210076</v>
+        <v>0.007941648349604849</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>0.5856171672710033</v>
+        <v>0.869610494281731</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -13837,13 +13837,13 @@
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.592051125866229e-05</v>
+        <v>2.365134061388612e-05</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.002674050992105038</v>
+        <v>0.003970824174802425</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13852,13 +13852,13 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0.002025661409633783</v>
+        <v>0.002026369472825973</v>
       </c>
       <c r="AF83" t="n">
-        <v>0.001909605518804226</v>
+        <v>0.007103244382843643</v>
       </c>
       <c r="AG83" t="n">
-        <v>8.805067545264276e-05</v>
+        <v>0.000367319739306008</v>
       </c>
       <c r="AH83" t="n">
         <v>0</v>
@@ -13882,7 +13882,7 @@
         <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>1.957338751199181e-05</v>
+        <v>0.0002260287628192135</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -13949,13 +13949,13 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.005348101984210076</v>
+        <v>0.007941648349604849</v>
       </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0.5856171672710033</v>
+        <v>0.869610494281731</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -13970,13 +13970,13 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.592051125866229e-05</v>
+        <v>2.365134061388612e-05</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.002674050992105038</v>
+        <v>0.003970824174802425</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13985,13 +13985,13 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.002025661409633783</v>
+        <v>0.002026369472825973</v>
       </c>
       <c r="AF84" t="n">
-        <v>0.001909605518804226</v>
+        <v>0.007103244382843643</v>
       </c>
       <c r="AG84" t="n">
-        <v>8.805067545264276e-05</v>
+        <v>0.000367319739306008</v>
       </c>
       <c r="AH84" t="n">
         <v>0</v>
@@ -14015,7 +14015,7 @@
         <v>0</v>
       </c>
       <c r="AO84" t="n">
-        <v>1.957338751199181e-05</v>
+        <v>0.0002260287628192135</v>
       </c>
       <c r="AP84" t="n">
         <v>0</v>
@@ -14103,7 +14103,7 @@
         <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>9.292723108654603e-05</v>
+        <v>0.0001482059276655101</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -14215,13 +14215,13 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0006663133661775077</v>
+        <v>0.000989021154827144</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>3.69737286891899</v>
+        <v>5.488078388135823</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -14236,7 +14236,7 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>3.398480144648209e-06</v>
+        <v>5.050841969780978e-06</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -14251,7 +14251,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="AO86" t="n">
-        <v>5.138422904040175e-05</v>
+        <v>0.0005933726960295194</v>
       </c>
       <c r="AP86" t="n">
         <v>0</v>
@@ -14348,13 +14348,13 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0006663133661775077</v>
+        <v>0.000989021154827144</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>3.69737286891899</v>
+        <v>5.488078388135823</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -14369,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>3.398480144648209e-06</v>
+        <v>5.050841969780978e-06</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -14384,7 +14384,7 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.8074306635414499</v>
+        <v>0.8077128982379166</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -14414,7 +14414,7 @@
         <v>0</v>
       </c>
       <c r="AO87" t="n">
-        <v>5.138422904040175e-05</v>
+        <v>0.0005933726960295194</v>
       </c>
       <c r="AP87" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.0006750684471292648</v>
+        <v>0.001066165429740137</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -14614,13 +14614,13 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.9148650130163603</v>
+        <v>0.9179547819916993</v>
       </c>
       <c r="T89" t="n">
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>1.124314069510288</v>
+        <v>1.128111209723417</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -14747,13 +14747,13 @@
         <v>0.006234</v>
       </c>
       <c r="S90" t="n">
-        <v>0.4649769364799838</v>
+        <v>0.4649769364799967</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>8.963894338398227</v>
+        <v>8.963921865831969</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -14886,7 +14886,7 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>0.006508013875697122</v>
+        <v>0.006509462687998574</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -15034,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.01840863390819256</v>
+        <v>0.003337418598482597</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -15167,10 +15167,10 @@
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.106098742692405</v>
+        <v>1.720667027853492</v>
       </c>
       <c r="AA93" t="n">
-        <v>4.035555691031838</v>
+        <v>6.277508476626917</v>
       </c>
       <c r="AB93" t="n">
         <v>0</v>
@@ -15182,10 +15182,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0.0008082389024439394</v>
+        <v>0.0008085214196576189</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.907695913285422e-24</v>
+        <v>7.0961411384608e-24</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -15212,7 +15212,7 @@
         <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>2.691032317783394e-05</v>
+        <v>0.0003107539280681235</v>
       </c>
       <c r="AP93" t="n">
         <v>0</v>
@@ -15433,10 +15433,10 @@
         <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.106222995082726</v>
+        <v>1.720785131054865</v>
       </c>
       <c r="AA95" t="n">
-        <v>4.035555691031838</v>
+        <v>6.277508476626917</v>
       </c>
       <c r="AB95" t="n">
         <v>0</v>
@@ -15448,10 +15448,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0.0007678269571397932</v>
+        <v>0.0007680953484896853</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.81231111719919e-24</v>
+        <v>6.741334079745978e-24</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>2.556480701298996e-05</v>
+        <v>0.0002952162314128801</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -15566,10 +15566,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.088477423453831</v>
+        <v>1.718572682794999</v>
       </c>
       <c r="AA96" t="n">
-        <v>4.035555691031838</v>
+        <v>6.277508476626917</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>
@@ -15581,13 +15581,13 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0.8102645638535276</v>
+        <v>0.8105477891304002</v>
       </c>
       <c r="AF96" t="n">
-        <v>0.001909605518804226</v>
+        <v>0.007103244382843643</v>
       </c>
       <c r="AG96" t="n">
-        <v>8.805067545264276e-05</v>
+        <v>0.000367319739306008</v>
       </c>
       <c r="AH96" t="n">
         <v>0</v>
@@ -15611,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="AO96" t="n">
-        <v>9.78679397302275e-05</v>
+        <v>0.001130155386916856</v>
       </c>
       <c r="AP96" t="n">
         <v>0</v>
@@ -15678,13 +15678,13 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0.005348101984210076</v>
+        <v>0.007941648349604849</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>0.5856171672710033</v>
+        <v>0.869610494281731</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -15705,7 +15705,7 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0.002674050992105038</v>
+        <v>0.003970824174802425</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -16196,10 +16196,10 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1834666680990804</v>
+        <v>0.1951545120208661</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.680275021793869</v>
+        <v>0.7129210398787297</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -16211,10 +16211,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1362451119672418</v>
+        <v>0.09182176868620129</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.215809614200853e-25</v>
+        <v>8.058911172153517e-25</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -16241,7 +16241,7 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.319813980884084e-05</v>
+        <v>0.0001026794142028914</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -16329,10 +16329,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1834666680990804</v>
+        <v>0.1951545120208661</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.680275021793869</v>
+        <v>0.7129210398787297</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -16344,10 +16344,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1362451119672418</v>
+        <v>0.09182176868620129</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.215809614200853e-25</v>
+        <v>8.058911172153517e-25</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -16374,7 +16374,7 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.319813980884084e-05</v>
+        <v>0.0001026794142028914</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -16447,7 +16447,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9998198198198197</v>
+        <v>0.9998198198198198</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9998198198198197</v>
+        <v>0.9998198198198198</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -16707,13 +16707,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001478659205058376</v>
+        <v>0.0001570262455383735</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8205079928868928</v>
+        <v>0.8713386364924344</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001505629960714284</v>
+        <v>0.0001700763107899561</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -16743,7 +16743,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1791821751890079</v>
+        <v>0.1282400515541909</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -16773,7 +16773,7 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.140300752201581e-05</v>
+        <v>9.420939704649958e-05</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -16861,10 +16861,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2122702821444764</v>
+        <v>0.214774733239812</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7875667326814159</v>
+        <v>0.7850852866055723</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -16876,10 +16876,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0001577334375631009</v>
+        <v>0.0001011162745286677</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.723001124020508e-25</v>
+        <v>8.874661054182419e-25</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -16906,7 +16906,7 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>5.251736544651354e-06</v>
+        <v>3.88638800870662e-05</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2150901280110942</v>
+        <v>0.2151023402953605</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7847474702548526</v>
+        <v>0.7847577379517184</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -17009,10 +17009,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0001571687972152027</v>
+        <v>0.0001010740873928627</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.709673850600429e-25</v>
+        <v>8.870958420428733e-25</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -17039,7 +17039,7 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.232936838035846e-06</v>
+        <v>3.884766552818548e-05</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -17127,10 +17127,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2150901280110942</v>
+        <v>0.2151023402953604</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7847474702548526</v>
+        <v>0.7847577379517184</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -17142,10 +17142,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001571687972152027</v>
+        <v>0.0001010740873928626</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.709673850600429e-25</v>
+        <v>8.870958420428733e-25</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -17172,7 +17172,7 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.232936838035846e-06</v>
+        <v>3.884766552818548e-05</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -17260,10 +17260,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.2150901280110941</v>
+        <v>0.2151023402953605</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.7847474702548526</v>
+        <v>0.7847577379517184</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -17275,10 +17275,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0001571687972152027</v>
+        <v>0.0001010740873928627</v>
       </c>
       <c r="AF11" t="n">
-        <v>3.709673850600429e-25</v>
+        <v>8.870958420428733e-25</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -17305,7 +17305,7 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>5.232936838035846e-06</v>
+        <v>3.884766552818548e-05</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -17393,10 +17393,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2155042246557526</v>
+        <v>0.2153641648597014</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.7844957753442473</v>
+        <v>0.7846358351402987</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -17499,19 +17499,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.165404360181527e-06</v>
+        <v>1.168115361318599e-06</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0006569202596684112</v>
+        <v>0.0006584484087227438</v>
       </c>
       <c r="S13" t="n">
-        <v>0.04899787774338359</v>
+        <v>0.04911185818383544</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9445883536125704</v>
+        <v>0.9467885929534919</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -17526,7 +17526,7 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001869975220150434</v>
+        <v>0.000233683515574344</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -17541,37 +17541,37 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0001178363733646894</v>
+        <v>8.822397689929929e-05</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0006058139374117074</v>
+        <v>5.865996011549809e-05</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.324858734878269e-05</v>
+        <v>3.828935662199605e-06</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.39139035691568e-05</v>
+        <v>3.399279518332941e-05</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.001322959845495261</v>
+        <v>0.001326037357273987</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0002665947644880893</v>
+        <v>0.0002672149258109386</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.861182128114542e-05</v>
+        <v>3.870164134272584e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.239029562621506e-05</v>
+        <v>2.244238065264536e-05</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0009003997347242992</v>
+        <v>0.0009024942735711217</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0002206828456918992</v>
+        <v>0.0002211962052313382</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0003232556508657415</v>
+        <v>0.0002434563712711519</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -17638,13 +17638,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.008946440238376777</v>
+        <v>0.008909008178297964</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.979635206102257</v>
+        <v>0.9755363955236271</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -17659,13 +17659,13 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0001820832558632427</v>
+        <v>0.000192790934727961</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.004473220119188388</v>
+        <v>0.004454504089148982</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -17674,13 +17674,13 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.003388577629592719</v>
+        <v>0.002273198385390381</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.003194436400670068</v>
+        <v>0.00796847952885648</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0001472933964631806</v>
+        <v>0.0004120623852213663</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -17704,7 +17704,7 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>3.274285758866084e-05</v>
+        <v>0.0002535609747297787</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -17765,19 +17765,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.226452598114621e-06</v>
+        <v>1.227919098490573e-06</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0006913321991509955</v>
+        <v>0.0006921588425382104</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02276213927712805</v>
+        <v>0.02261253246744276</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9724444096055906</v>
+        <v>0.9733137561903473</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -17792,7 +17792,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.163680420889329e-05</v>
+        <v>9.926163889488407e-06</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -17807,37 +17807,37 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.000124009083201831</v>
+        <v>9.274075983142008e-05</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0006375487366435663</v>
+        <v>6.166316078679627e-05</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.499027267342963e-05</v>
+        <v>4.024964812721267e-06</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.569044064510128e-05</v>
+        <v>3.573311660722526e-05</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.00139226142886255</v>
+        <v>0.001393926191049031</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0002805599950726486</v>
+        <v>0.0002808954677512374</v>
       </c>
       <c r="AK15" t="n">
-        <v>4.063445285276084e-05</v>
+        <v>4.068304049526476e-05</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.356318303035051e-05</v>
+        <v>2.359135812397076e-05</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0009475660395009347</v>
+        <v>0.0009486990681685778</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0002322430383013146</v>
+        <v>0.0002325207371732523</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0003401889905386726</v>
+        <v>0.0002559205518841928</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -17904,13 +17904,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3048594552617723</v>
+        <v>0.3048585840009939</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6951405447382277</v>
+        <v>0.695141415999006</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -18037,13 +18037,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5711657782042513</v>
+        <v>0.5693307587367707</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4288342217957488</v>
+        <v>0.4306692412632293</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -18170,13 +18170,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005122742430807832</v>
+        <v>0.005620969349804777</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9811728981945462</v>
+        <v>0.9765579836224452</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -18191,7 +18191,7 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.703636134293689e-05</v>
+        <v>2.68417296482251e-05</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -18200,19 +18200,19 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.004541098441964566</v>
+        <v>0.00450645867059671</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.002270549220982283</v>
+        <v>0.002253229335298355</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.00343999717970763</v>
+        <v>0.002299711565824608</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.003242909978834158</v>
+        <v>0.008061418947119675</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.0001495284818024957</v>
+        <v>0.0004168684261018044</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -18236,7 +18236,7 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>3.323971001192608e-05</v>
+        <v>0.0002565183531606693</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -18303,13 +18303,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2290407880054399</v>
+        <v>0.2467155979920801</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7709592119945601</v>
+        <v>0.7532844020079199</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -18436,13 +18436,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5636745323364148</v>
+        <v>0.5610347486137375</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4363254676635852</v>
+        <v>0.4389652513862625</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -18569,13 +18569,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5636745323364148</v>
+        <v>0.5610347486137375</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4363254676635852</v>
+        <v>0.4389652513862625</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -18702,13 +18702,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5636745323364148</v>
+        <v>0.5610347486137375</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4363254676635852</v>
+        <v>0.4389652513862625</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -18835,13 +18835,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.659724671617105e-05</v>
+        <v>7.2871204856793e-05</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3140581220280331</v>
+        <v>0.4043623157503444</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -18856,7 +18856,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.886699096404173e-06</v>
+        <v>3.721466806678421e-06</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.685838747807484</v>
+        <v>0.5951238938185938</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -18901,7 +18901,7 @@
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>4.364621867040718e-05</v>
+        <v>0.0004371977593983003</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -18968,13 +18968,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.659724671617105e-05</v>
+        <v>7.2871204856793e-05</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3140581220280331</v>
+        <v>0.4043623157503444</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -18989,7 +18989,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.886699096404173e-06</v>
+        <v>3.721466806678421e-06</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -19004,7 +19004,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.685838747807484</v>
+        <v>0.5951238938185938</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -19034,7 +19034,7 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>4.364621867040718e-05</v>
+        <v>0.0004371977593983003</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -19769,10 +19769,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.6761511944271685</v>
+        <v>0.6290378231992545</v>
       </c>
       <c r="U30" t="n">
-        <v>0.1548110069660392</v>
+        <v>0.2137027210009318</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -19784,7 +19784,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1690377986067921</v>
+        <v>0.1572594557998136</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -19902,10 +19902,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.6761511944271685</v>
+        <v>0.6290378231992545</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1548110069660392</v>
+        <v>0.2137027210009318</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -19917,7 +19917,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1690377986067921</v>
+        <v>0.1572594557998136</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -20431,13 +20431,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.3048594552617723</v>
+        <v>0.3048585840009939</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0.6951405447382277</v>
+        <v>0.695141415999006</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -20564,13 +20564,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.3048594552617723</v>
+        <v>0.3048585840009939</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.6951405447382277</v>
+        <v>0.695141415999006</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -21229,13 +21229,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.04249057995202787</v>
+        <v>0.0332350002993952</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2612430476510548</v>
+        <v>0.2024507750737733</v>
       </c>
       <c r="U41" t="n">
-        <v>0.6309556104841536</v>
+        <v>0.7137015308583882</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -21247,7 +21247,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.06531076191276369</v>
+        <v>0.05061269376844333</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -21362,13 +21362,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.04249057995202787</v>
+        <v>0.0332350002993952</v>
       </c>
       <c r="T42" t="n">
-        <v>0.2612430476510548</v>
+        <v>0.2024507750737733</v>
       </c>
       <c r="U42" t="n">
-        <v>0.6309556104841536</v>
+        <v>0.7137015308583882</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -21380,7 +21380,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.06531076191276369</v>
+        <v>0.05061269376844333</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -21495,13 +21495,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.06309424651211901</v>
+        <v>0.04449507945190409</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0.9369057534878811</v>
+        <v>0.9555049205480959</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -21631,7 +21631,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.8</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -21761,13 +21761,13 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.188797965399045</v>
+        <v>0.188814357430994</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0.8112020346009551</v>
+        <v>0.811185642569006</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -21894,13 +21894,13 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1567679914613943</v>
+        <v>0.1413877985925763</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0.8432320085386057</v>
+        <v>0.8586122014074237</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -22027,13 +22027,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.1567679914613943</v>
+        <v>0.1413877985925763</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0.8432320085386057</v>
+        <v>0.8586122014074237</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -22807,16 +22807,16 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.002801949718651501</v>
+        <v>0.002801548588709665</v>
       </c>
       <c r="N53" t="n">
-        <v>0.0004948645459410178</v>
+        <v>0.0004947937006345483</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.0001099672515973454</v>
+        <v>0.0001099515085749266</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -22828,7 +22828,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0.391441191749774</v>
+        <v>0.3914996814399704</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -22837,13 +22837,13 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.08985703739137918</v>
+        <v>0.0898441733674667</v>
       </c>
       <c r="X53" t="n">
-        <v>0.3423629915557441</v>
+        <v>0.3423139785252906</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.1729319977869128</v>
+        <v>0.1729358728693531</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -22940,16 +22940,16 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.002801949718651501</v>
+        <v>0.002801548588709665</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0004948645459410178</v>
+        <v>0.0004947937006345483</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0001099672515973454</v>
+        <v>0.0001099515085749266</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -22961,7 +22961,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0.391441191749774</v>
+        <v>0.3914996814399704</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -22970,13 +22970,13 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.08985703739137918</v>
+        <v>0.0898441733674667</v>
       </c>
       <c r="X54" t="n">
-        <v>0.3423629915557441</v>
+        <v>0.3423139785252906</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.1729319977869128</v>
+        <v>0.1729358728693531</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -23073,16 +23073,16 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.007422244452461558</v>
+        <v>0.007422151273120887</v>
       </c>
       <c r="N55" t="n">
-        <v>0.001310874926263252</v>
+        <v>0.001310858469453979</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.0002912985260540853</v>
+        <v>0.0002912948690734011</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -23094,7 +23094,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.01036910903357667</v>
+        <v>0.0103720130742563</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -23103,13 +23103,13 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02901040152626312</v>
+        <v>0.02901504378278927</v>
       </c>
       <c r="X55" t="n">
-        <v>0.9069048591013706</v>
+        <v>0.9068934737586535</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.04469121243401072</v>
+        <v>0.04469516477265273</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -23206,16 +23206,16 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.007422244452461558</v>
+        <v>0.007422151273120887</v>
       </c>
       <c r="N56" t="n">
-        <v>0.001310874926263252</v>
+        <v>0.001310858469453979</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.0002912985260540853</v>
+        <v>0.0002912948690734011</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -23227,7 +23227,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.01036910903357667</v>
+        <v>0.0103720130742563</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -23236,13 +23236,13 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02901040152626312</v>
+        <v>0.02901504378278927</v>
       </c>
       <c r="X56" t="n">
-        <v>0.9069048591013706</v>
+        <v>0.9068934737586535</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.04469121243401072</v>
+        <v>0.04469516477265273</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -23605,16 +23605,16 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.006935620080647616</v>
+        <v>0.006935435287881313</v>
       </c>
       <c r="N59" t="n">
-        <v>0.001224930076076063</v>
+        <v>0.001224897439020594</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0002722001302575975</v>
+        <v>0.000272192877753211</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -23626,22 +23626,22 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.0006046110392402575</v>
+        <v>0.0006047718491410017</v>
       </c>
       <c r="U59" t="n">
-        <v>0.06537924994514799</v>
+        <v>0.06539206230269481</v>
       </c>
       <c r="V59" t="n">
-        <v>0.006537924994514797</v>
+        <v>0.006539206230269477</v>
       </c>
       <c r="W59" t="n">
-        <v>0.001691563755263253</v>
+        <v>0.00169181060183756</v>
       </c>
       <c r="X59" t="n">
-        <v>0.8864893177107139</v>
+        <v>0.8864740717961662</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.03086458226813852</v>
+        <v>0.03086555161523583</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -23738,16 +23738,16 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.006935620080647616</v>
+        <v>0.006935435287881313</v>
       </c>
       <c r="N60" t="n">
-        <v>0.001224930076076063</v>
+        <v>0.001224897439020594</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.0002722001302575975</v>
+        <v>0.000272192877753211</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -23759,22 +23759,22 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.0006046110392402575</v>
+        <v>0.0006047718491410017</v>
       </c>
       <c r="U60" t="n">
-        <v>0.06537924994514799</v>
+        <v>0.06539206230269481</v>
       </c>
       <c r="V60" t="n">
-        <v>0.006537924994514797</v>
+        <v>0.006539206230269477</v>
       </c>
       <c r="W60" t="n">
-        <v>0.001691563755263253</v>
+        <v>0.00169181060183756</v>
       </c>
       <c r="X60" t="n">
-        <v>0.8864893177107139</v>
+        <v>0.8864740717961662</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.03086458226813852</v>
+        <v>0.03086555161523583</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -24137,16 +24137,16 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.007420785468587736</v>
+        <v>0.007420689476454583</v>
       </c>
       <c r="N63" t="n">
-        <v>0.001310617248765527</v>
+        <v>0.00131060029517672</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0002912412657664858</v>
+        <v>0.0002912374983930075</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -24158,22 +24158,22 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.0006469052171212479</v>
+        <v>0.0006470861467655022</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.006995270535274432</v>
+        <v>0.006996737312525749</v>
       </c>
       <c r="W63" t="n">
-        <v>0.001809893216220565</v>
+        <v>0.001810182145473595</v>
       </c>
       <c r="X63" t="n">
-        <v>0.9485016437508869</v>
+        <v>0.9484983339433949</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.03302364329737715</v>
+        <v>0.03302513318181593</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -24560,10 +24560,10 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0.9989781032687934</v>
+        <v>0.9989778892151933</v>
       </c>
       <c r="V66" t="n">
-        <v>0.001021896731206606</v>
+        <v>0.001022110784806729</v>
       </c>
       <c r="W66" t="n">
         <v>0</v>
@@ -24669,16 +24669,16 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.007472535149493238</v>
+        <v>0.007472449414432162</v>
       </c>
       <c r="N67" t="n">
-        <v>0.001319756985347316</v>
+        <v>0.001319741843304692</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0002932722694430816</v>
+        <v>0.0002932689046257299</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -24690,22 +24690,22 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.0006514164833078043</v>
+        <v>0.0006515996274776387</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>7.044052840002248e-05</v>
+        <v>7.04554014823132e-05</v>
       </c>
       <c r="W67" t="n">
-        <v>0.001822514709835886</v>
+        <v>0.001822808319345325</v>
       </c>
       <c r="X67" t="n">
-        <v>0.9551161264913229</v>
+        <v>0.9551141902048004</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.03325393738284969</v>
+        <v>0.03325548628453177</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -24802,16 +24802,16 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.007472535149493238</v>
+        <v>0.007472449414432162</v>
       </c>
       <c r="N68" t="n">
-        <v>0.001319756985347316</v>
+        <v>0.001319741843304692</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0002932722694430816</v>
+        <v>0.0002932689046257299</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -24823,22 +24823,22 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.0006514164833078043</v>
+        <v>0.0006515996274776387</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>7.044052840002248e-05</v>
+        <v>7.04554014823132e-05</v>
       </c>
       <c r="W68" t="n">
-        <v>0.001822514709835886</v>
+        <v>0.001822808319345325</v>
       </c>
       <c r="X68" t="n">
-        <v>0.9551161264913229</v>
+        <v>0.9551141902048004</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.03325393738284969</v>
+        <v>0.03325548628453177</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -25080,19 +25080,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.075443020314617e-06</v>
+        <v>1.075440141533842e-06</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0006062104556169797</v>
+        <v>0.000606208832893161</v>
       </c>
       <c r="S70" t="n">
-        <v>0.04521557274862342</v>
+        <v>0.04521545171411233</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>0.8716725170007786</v>
+        <v>0.871672860511948</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -25122,37 +25122,37 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0.07882631891438494</v>
+        <v>0.07882610790953661</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.0007447442283601721</v>
+        <v>0.0007447422348046552</v>
       </c>
       <c r="AG70" t="n">
-        <v>3.924429897077319e-05</v>
+        <v>3.924419392036026e-05</v>
       </c>
       <c r="AH70" t="n">
-        <v>3.129597943102904e-05</v>
+        <v>3.129589565693577e-05</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.0012208362870487</v>
+        <v>0.001220833019074512</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0002460154505312441</v>
+        <v>0.0002460147919891031</v>
       </c>
       <c r="AK70" t="n">
-        <v>3.563124964795496e-05</v>
+        <v>3.563115426906969e-05</v>
       </c>
       <c r="AL70" t="n">
-        <v>2.066191613548037e-05</v>
+        <v>2.066186082699279e-05</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.0008308949608284886</v>
+        <v>0.0008308927366618954</v>
       </c>
       <c r="AN70" t="n">
-        <v>0.000203647621556481</v>
+        <v>0.0002036470764259194</v>
       </c>
       <c r="AO70" t="n">
-        <v>0.0003053334450654689</v>
+        <v>0.0003053326277389953</v>
       </c>
       <c r="AP70" t="n">
         <v>0</v>
@@ -25213,19 +25213,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.075443020314617e-06</v>
+        <v>1.075440141533842e-06</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0006062104556169797</v>
+        <v>0.000606208832893161</v>
       </c>
       <c r="S71" t="n">
-        <v>0.04521557274862342</v>
+        <v>0.04521545171411233</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>0.8716725170007786</v>
+        <v>0.871672860511948</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -25255,37 +25255,37 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0.07882631891438494</v>
+        <v>0.07882610790953661</v>
       </c>
       <c r="AF71" t="n">
-        <v>0.0007447442283601721</v>
+        <v>0.0007447422348046552</v>
       </c>
       <c r="AG71" t="n">
-        <v>3.924429897077319e-05</v>
+        <v>3.924419392036026e-05</v>
       </c>
       <c r="AH71" t="n">
-        <v>3.129597943102904e-05</v>
+        <v>3.129589565693577e-05</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.0012208362870487</v>
+        <v>0.001220833019074512</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.0002460154505312441</v>
+        <v>0.0002460147919891031</v>
       </c>
       <c r="AK71" t="n">
-        <v>3.563124964795496e-05</v>
+        <v>3.563115426906969e-05</v>
       </c>
       <c r="AL71" t="n">
-        <v>2.066191613548037e-05</v>
+        <v>2.066186082699279e-05</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0008308949608284886</v>
+        <v>0.0008308927366618954</v>
       </c>
       <c r="AN71" t="n">
-        <v>0.000203647621556481</v>
+        <v>0.0002036470764259194</v>
       </c>
       <c r="AO71" t="n">
-        <v>0.0003053334450654689</v>
+        <v>0.0003053326277389953</v>
       </c>
       <c r="AP71" t="n">
         <v>0</v>
@@ -25334,10 +25334,10 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0.007474727279726032</v>
+        <v>0.007474641494355681</v>
       </c>
       <c r="N72" t="n">
-        <v>0.001320144147017304</v>
+        <v>0.00132012899608934</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -25355,22 +25355,22 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0.0006516075817420881</v>
+        <v>0.0006517907774449852</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>7.046119271391736e-05</v>
+        <v>7.047606992214158e-05</v>
       </c>
       <c r="W72" t="n">
-        <v>0.0018230493596589</v>
+        <v>0.00182334304916411</v>
       </c>
       <c r="X72" t="n">
-        <v>0.9553963177376434</v>
+        <v>0.9553943776674244</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.03326369270149832</v>
+        <v>0.03326524194559926</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -26144,19 +26144,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.167574785561221e-06</v>
+        <v>1.168377359179266e-06</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0006581436946002979</v>
+        <v>0.0006585960928301166</v>
       </c>
       <c r="S78" t="n">
-        <v>0.04908913039442808</v>
+        <v>0.04912287353574642</v>
       </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>0.9463475357523423</v>
+        <v>0.9470009491933564</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -26171,7 +26171,7 @@
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.107816086793983e-05</v>
+        <v>9.444844669520451e-06</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -26186,37 +26186,37 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.0001180558294300176</v>
+        <v>8.824376475071581e-05</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.0006069421929683673</v>
+        <v>5.867311702154178e-05</v>
       </c>
       <c r="AG78" t="n">
-        <v>3.331050884168796e-05</v>
+        <v>3.829794458329976e-06</v>
       </c>
       <c r="AH78" t="n">
-        <v>3.397706413346043e-05</v>
+        <v>3.400041946421042e-05</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.001325423699006613</v>
+        <v>0.001326334775630319</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.0002670912651557616</v>
+        <v>0.0002672748597363188</v>
       </c>
       <c r="AK78" t="n">
-        <v>3.868373115185479e-05</v>
+        <v>3.87103217758165e-05</v>
       </c>
       <c r="AL78" t="n">
-        <v>2.243199485744018e-05</v>
+        <v>2.244741427853024e-05</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.000902076620878913</v>
+        <v>0.0009026966949900754</v>
       </c>
       <c r="AN78" t="n">
-        <v>0.0002210938409357115</v>
+        <v>0.0002212458175679937</v>
       </c>
       <c r="AO78" t="n">
-        <v>0.0003238576756158969</v>
+        <v>0.0002435109763645793</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -26277,19 +26277,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.167574785561221e-06</v>
+        <v>1.168377359179266e-06</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0006581436946002979</v>
+        <v>0.0006585960928301166</v>
       </c>
       <c r="S79" t="n">
-        <v>0.04908913039442808</v>
+        <v>0.04912287353574642</v>
       </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>0.9463475357523423</v>
+        <v>0.9470009491933564</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -26304,7 +26304,7 @@
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.107816086793983e-05</v>
+        <v>9.444844669520451e-06</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -26319,37 +26319,37 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0.0001180558294300176</v>
+        <v>8.824376475071581e-05</v>
       </c>
       <c r="AF79" t="n">
-        <v>0.0006069421929683673</v>
+        <v>5.867311702154178e-05</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.331050884168796e-05</v>
+        <v>3.829794458329976e-06</v>
       </c>
       <c r="AH79" t="n">
-        <v>3.397706413346043e-05</v>
+        <v>3.400041946421042e-05</v>
       </c>
       <c r="AI79" t="n">
-        <v>0.001325423699006613</v>
+        <v>0.001326334775630319</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.0002670912651557616</v>
+        <v>0.0002672748597363188</v>
       </c>
       <c r="AK79" t="n">
-        <v>3.868373115185479e-05</v>
+        <v>3.87103217758165e-05</v>
       </c>
       <c r="AL79" t="n">
-        <v>2.243199485744018e-05</v>
+        <v>2.244741427853024e-05</v>
       </c>
       <c r="AM79" t="n">
-        <v>0.000902076620878913</v>
+        <v>0.0009026966949900754</v>
       </c>
       <c r="AN79" t="n">
-        <v>0.0002210938409357115</v>
+        <v>0.0002212458175679937</v>
       </c>
       <c r="AO79" t="n">
-        <v>0.0003238576756158969</v>
+        <v>0.0002435109763645793</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -26410,19 +26410,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.167574785561221e-06</v>
+        <v>1.168377359179266e-06</v>
       </c>
       <c r="R80" t="n">
-        <v>0.0006581436946002979</v>
+        <v>0.0006585960928301166</v>
       </c>
       <c r="S80" t="n">
-        <v>0.04908913039442808</v>
+        <v>0.04912287353574642</v>
       </c>
       <c r="T80" t="n">
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>0.9463475357523423</v>
+        <v>0.9470009491933564</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -26437,7 +26437,7 @@
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.107816086793983e-05</v>
+        <v>9.444844669520451e-06</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -26452,37 +26452,37 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0.0001180558294300176</v>
+        <v>8.824376475071581e-05</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.0006069421929683673</v>
+        <v>5.867311702154178e-05</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.331050884168796e-05</v>
+        <v>3.829794458329976e-06</v>
       </c>
       <c r="AH80" t="n">
-        <v>3.397706413346043e-05</v>
+        <v>3.400041946421042e-05</v>
       </c>
       <c r="AI80" t="n">
-        <v>0.001325423699006613</v>
+        <v>0.001326334775630319</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.0002670912651557616</v>
+        <v>0.0002672748597363188</v>
       </c>
       <c r="AK80" t="n">
-        <v>3.868373115185479e-05</v>
+        <v>3.87103217758165e-05</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.243199485744018e-05</v>
+        <v>2.244741427853024e-05</v>
       </c>
       <c r="AM80" t="n">
-        <v>0.000902076620878913</v>
+        <v>0.0009026966949900754</v>
       </c>
       <c r="AN80" t="n">
-        <v>0.0002210938409357115</v>
+        <v>0.0002212458175679937</v>
       </c>
       <c r="AO80" t="n">
-        <v>0.0003238576756158969</v>
+        <v>0.0002435109763645793</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -26682,13 +26682,13 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.008947831187879996</v>
+        <v>0.008910489624372783</v>
       </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>0.9797875150728595</v>
+        <v>0.9756986138688198</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -26703,13 +26703,13 @@
         <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.663637447225939e-05</v>
+        <v>2.653668556767877e-05</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.004473915593939998</v>
+        <v>0.004455244812186392</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -26718,13 +26718,13 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.003389104469346289</v>
+        <v>0.00227357638715645</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.003194933056279025</v>
+        <v>0.007969804577894942</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.0001473162969321022</v>
+        <v>0.0004121309055539275</v>
       </c>
       <c r="AH82" t="n">
         <v>0</v>
@@ -26748,7 +26748,7 @@
         <v>0</v>
       </c>
       <c r="AO82" t="n">
-        <v>3.274794829069243e-05</v>
+        <v>0.0002536031384480314</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -26815,13 +26815,13 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.008947831187879996</v>
+        <v>0.008910489624372783</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>0.9797875150728595</v>
+        <v>0.9756986138688198</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -26836,13 +26836,13 @@
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.663637447225939e-05</v>
+        <v>2.653668556767877e-05</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.004473915593939998</v>
+        <v>0.004455244812186392</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -26851,13 +26851,13 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0.003389104469346289</v>
+        <v>0.00227357638715645</v>
       </c>
       <c r="AF83" t="n">
-        <v>0.003194933056279025</v>
+        <v>0.007969804577894942</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.0001473162969321022</v>
+        <v>0.0004121309055539275</v>
       </c>
       <c r="AH83" t="n">
         <v>0</v>
@@ -26881,7 +26881,7 @@
         <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>3.274794829069243e-05</v>
+        <v>0.0002536031384480314</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -26948,13 +26948,13 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.008947831187879996</v>
+        <v>0.008910489624372783</v>
       </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0.9797875150728595</v>
+        <v>0.9756986138688198</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -26969,13 +26969,13 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.663637447225939e-05</v>
+        <v>2.653668556767877e-05</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.004473915593939998</v>
+        <v>0.004455244812186392</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -26984,13 +26984,13 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.003389104469346289</v>
+        <v>0.00227357638715645</v>
       </c>
       <c r="AF84" t="n">
-        <v>0.003194933056279025</v>
+        <v>0.007969804577894942</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.0001473162969321022</v>
+        <v>0.0004121309055539275</v>
       </c>
       <c r="AH84" t="n">
         <v>0</v>
@@ -27014,7 +27014,7 @@
         <v>0</v>
       </c>
       <c r="AO84" t="n">
-        <v>3.274794829069243e-05</v>
+        <v>0.0002536031384480314</v>
       </c>
       <c r="AP84" t="n">
         <v>0</v>
@@ -27214,13 +27214,13 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001478880754435128</v>
+        <v>0.000157052830560762</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>0.8206309306360524</v>
+        <v>0.8714861567816686</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -27235,7 +27235,7 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>7.54291769514229e-07</v>
+        <v>8.020546620237234e-07</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -27250,7 +27250,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.1792090222806855</v>
+        <v>0.1282617629861237</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -27280,7 +27280,7 @@
         <v>0</v>
       </c>
       <c r="AO86" t="n">
-        <v>1.140471604903878e-05</v>
+        <v>9.422534698481154e-05</v>
       </c>
       <c r="AP86" t="n">
         <v>0</v>
@@ -27347,13 +27347,13 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001478880754435128</v>
+        <v>0.000157052830560762</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>0.8206309306360524</v>
+        <v>0.8714861567816686</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>7.54291769514229e-07</v>
+        <v>8.020546620237234e-07</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -27383,7 +27383,7 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.1792090222806855</v>
+        <v>0.1282617629861237</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -27413,7 +27413,7 @@
         <v>0</v>
       </c>
       <c r="AO87" t="n">
-        <v>1.140471604903878e-05</v>
+        <v>9.422534698481154e-05</v>
       </c>
       <c r="AP87" t="n">
         <v>0</v>
@@ -27619,7 +27619,7 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>0.5513562193454852</v>
+        <v>0.5513562193454851</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -27740,19 +27740,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.075443020314617e-06</v>
+        <v>1.075440141533842e-06</v>
       </c>
       <c r="R90" t="n">
-        <v>0.0006062104556169797</v>
+        <v>0.000606208832893161</v>
       </c>
       <c r="S90" t="n">
-        <v>0.04521557274862342</v>
+        <v>0.04521545171411233</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>0.8716725170007786</v>
+        <v>0.871672860511948</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -27782,37 +27782,37 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.07882631891438494</v>
+        <v>0.07882610790953661</v>
       </c>
       <c r="AF90" t="n">
-        <v>0.0007447442283601721</v>
+        <v>0.0007447422348046552</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.924429897077319e-05</v>
+        <v>3.924419392036026e-05</v>
       </c>
       <c r="AH90" t="n">
-        <v>3.129597943102904e-05</v>
+        <v>3.129589565693577e-05</v>
       </c>
       <c r="AI90" t="n">
-        <v>0.0012208362870487</v>
+        <v>0.001220833019074512</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.0002460154505312441</v>
+        <v>0.0002460147919891031</v>
       </c>
       <c r="AK90" t="n">
-        <v>3.563124964795496e-05</v>
+        <v>3.563115426906969e-05</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.066191613548037e-05</v>
+        <v>2.066186082699279e-05</v>
       </c>
       <c r="AM90" t="n">
-        <v>0.0008308949608284886</v>
+        <v>0.0008308927366618954</v>
       </c>
       <c r="AN90" t="n">
-        <v>0.000203647621556481</v>
+        <v>0.0002036470764259194</v>
       </c>
       <c r="AO90" t="n">
-        <v>0.0003053334450654689</v>
+        <v>0.0003053326277389953</v>
       </c>
       <c r="AP90" t="n">
         <v>0</v>
@@ -28166,10 +28166,10 @@
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>0.2150901280110942</v>
+        <v>0.2151023402953605</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.7847474702548526</v>
+        <v>0.7847577379517184</v>
       </c>
       <c r="AB93" t="n">
         <v>0</v>
@@ -28181,10 +28181,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0.0001571687972152027</v>
+        <v>0.0001010740873928627</v>
       </c>
       <c r="AF93" t="n">
-        <v>3.709673850600429e-25</v>
+        <v>8.870958420428733e-25</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -28211,7 +28211,7 @@
         <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>5.232936838035846e-06</v>
+        <v>3.884766552818548e-05</v>
       </c>
       <c r="AP93" t="n">
         <v>0</v>
@@ -28432,10 +28432,10 @@
         <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.2151108391540594</v>
+        <v>0.2151154334558294</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.7847348816735463</v>
+        <v>0.7847516419115239</v>
       </c>
       <c r="AB95" t="n">
         <v>0</v>
@@ -28447,10 +28447,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0.0001493079621465447</v>
+        <v>9.601963710860124e-05</v>
       </c>
       <c r="AF95" t="n">
-        <v>3.524133623707532e-25</v>
+        <v>8.427345032590673e-25</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -28477,7 +28477,7 @@
         <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>4.971210247681216e-06</v>
+        <v>3.690499553808229e-05</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -28565,10 +28565,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>0.1833566925789815</v>
+        <v>0.1949549526794055</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.6797992574599959</v>
+        <v>0.7121208083064552</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>
@@ -28580,13 +28580,13 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0.1364910537792476</v>
+        <v>0.0919485730550062</v>
       </c>
       <c r="AF96" t="n">
-        <v>0.0003216777348927389</v>
+        <v>0.0008057923219606559</v>
       </c>
       <c r="AG96" t="n">
-        <v>1.483235231385273e-05</v>
+        <v>4.166876566323062e-05</v>
       </c>
       <c r="AH96" t="n">
         <v>0</v>
@@ -28610,7 +28610,7 @@
         <v>0</v>
       </c>
       <c r="AO96" t="n">
-        <v>1.648609456823958e-05</v>
+        <v>0.0001282048715090819</v>
       </c>
       <c r="AP96" t="n">
         <v>0</v>

--- a/stream_table.xlsx
+++ b/stream_table.xlsx
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.805334848435308</v>
+        <v>8.804575268857423</v>
       </c>
       <c r="F3" t="n">
-        <v>1845.637371653705</v>
+        <v>1845.342409605534</v>
       </c>
     </row>
     <row r="4">
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8.805334848435308</v>
+        <v>8.804575268857423</v>
       </c>
       <c r="F4" t="n">
-        <v>1845.637371653705</v>
+        <v>1845.342409605534</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.48906740929065</v>
+        <v>22.01143817214356</v>
       </c>
       <c r="F5" t="n">
-        <v>98.93005236327481</v>
+        <v>396.7145178934062</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.48906740929065</v>
+        <v>22.01143817214356</v>
       </c>
       <c r="F6" t="n">
-        <v>98.93005236327481</v>
+        <v>396.7145178934062</v>
       </c>
     </row>
     <row r="7">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.298444896496306</v>
+        <v>22.82439444860892</v>
       </c>
       <c r="F7" t="n">
-        <v>417.5313411172469</v>
+        <v>716.2480783334413</v>
       </c>
     </row>
     <row r="8">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.995957361229651</v>
+        <v>7.991618992392059</v>
       </c>
       <c r="F8" t="n">
-        <v>1527.036082899733</v>
+        <v>1525.808849165499</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.999294779828134</v>
+        <v>7.998165999562447</v>
       </c>
       <c r="F9" t="n">
-        <v>1527.924897546044</v>
+        <v>1527.552435021102</v>
       </c>
     </row>
     <row r="10">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3999647389914068</v>
+        <v>0.3999082999781223</v>
       </c>
       <c r="F10" t="n">
-        <v>76.39624487730219</v>
+        <v>76.37762175105509</v>
       </c>
     </row>
     <row r="11">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.599330040836727</v>
+        <v>7.598257699584324</v>
       </c>
       <c r="F11" t="n">
-        <v>1451.528652668741</v>
+        <v>1451.174813270047</v>
       </c>
     </row>
     <row r="12">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4000268806279962</v>
+        <v>0.4000415759223812</v>
       </c>
       <c r="F12" t="n">
-        <v>76.40922320067784</v>
+        <v>76.41311769563822</v>
       </c>
     </row>
     <row r="13">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.467712150892268</v>
+        <v>9.467428259553966</v>
       </c>
       <c r="F13" t="n">
-        <v>200.4286341162171</v>
+        <v>200.3754502030685</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8914177864322125</v>
+        <v>0.8913334180503505</v>
       </c>
       <c r="F14" t="n">
-        <v>20.98863404990027</v>
+        <v>20.98551975690453</v>
       </c>
     </row>
     <row r="15">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.006603133378098</v>
+        <v>9.00612933333662</v>
       </c>
       <c r="F15" t="n">
-        <v>179.8362127293603</v>
+        <v>179.7764324588741</v>
       </c>
     </row>
     <row r="16">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="F16" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
     <row r="17">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4589859702730928</v>
+        <v>0.4591758777492462</v>
       </c>
       <c r="F17" t="n">
-        <v>20.02701569170773</v>
+        <v>20.03361172226714</v>
       </c>
     </row>
     <row r="18">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8811407060517076</v>
+        <v>0.8810518086433173</v>
       </c>
       <c r="F18" t="n">
-        <v>20.62420100004125</v>
+        <v>20.6209753492418</v>
       </c>
     </row>
     <row r="19">
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01211428654024057</v>
+        <v>0.01211864061573059</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3527251608331186</v>
+        <v>0.3528335291401753</v>
       </c>
     </row>
     <row r="20">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="F20" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
     <row r="21">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="F21" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
     <row r="22">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4711002568133334</v>
+        <v>0.4712945183649768</v>
       </c>
       <c r="F22" t="n">
-        <v>20.37974085254085</v>
+        <v>20.38644525140731</v>
       </c>
     </row>
     <row r="23">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.357218062704981</v>
+        <v>3.009824343057617</v>
       </c>
       <c r="F23" t="n">
-        <v>328.2103549453821</v>
+        <v>358.0663028751986</v>
       </c>
     </row>
     <row r="24">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.357218062704981</v>
+        <v>3.009824343057617</v>
       </c>
       <c r="F24" t="n">
-        <v>328.2103549453821</v>
+        <v>358.0663028751986</v>
       </c>
     </row>
     <row r="25">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.940160668361585</v>
+        <v>19.8102943549292</v>
       </c>
       <c r="F25" t="n">
-        <v>89.03704712694733</v>
+        <v>357.0430661040656</v>
       </c>
     </row>
     <row r="26">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="F26" t="n">
-        <v>230.9784266575041</v>
+        <v>230.9975700434508</v>
       </c>
     </row>
     <row r="27">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="F27" t="n">
-        <v>230.9784266575041</v>
+        <v>230.9975700434508</v>
       </c>
     </row>
     <row r="28">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2692376327459722</v>
+        <v>0.2692599470373526</v>
       </c>
       <c r="F28" t="n">
-        <v>226.6708937712012</v>
+        <v>226.6896801508001</v>
       </c>
     </row>
     <row r="29">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.1346188163729861</v>
+        <v>0.1346299735186763</v>
       </c>
       <c r="F29" t="n">
-        <v>4.307532886302809</v>
+        <v>4.307889892650604</v>
       </c>
     </row>
     <row r="30">
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.568090084408374</v>
+        <v>4.220196817504912</v>
       </c>
       <c r="F30" t="n">
-        <v>97.12703564200582</v>
+        <v>126.893953931939</v>
       </c>
     </row>
     <row r="31">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.568090084408374</v>
+        <v>4.220196817504912</v>
       </c>
       <c r="F31" t="n">
-        <v>97.12703564200582</v>
+        <v>126.893953931939</v>
       </c>
     </row>
     <row r="32">
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.570568549995905</v>
+        <v>2.570568549995908</v>
       </c>
       <c r="F33" t="n">
-        <v>104.3582919498547</v>
+        <v>104.3582919498548</v>
       </c>
     </row>
     <row r="34">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.669566341355434</v>
+        <v>3.669566341355437</v>
       </c>
       <c r="F34" t="n">
-        <v>140.1870639088395</v>
+        <v>140.1870639088396</v>
       </c>
     </row>
     <row r="35">
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="F35" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
     <row r="36">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9.632016791071965</v>
+        <v>9.632023320267546</v>
       </c>
       <c r="F36" t="n">
-        <v>305.6501082821613</v>
+        <v>305.6502259056198</v>
       </c>
     </row>
     <row r="37">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.268202108648652</v>
+        <v>3.268202108648653</v>
       </c>
       <c r="F37" t="n">
-        <v>58.87666098730547</v>
+        <v>58.87666098730549</v>
       </c>
     </row>
     <row r="38">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3.391881899720625</v>
+        <v>3.391888428916202</v>
       </c>
       <c r="F38" t="n">
-        <v>61.10475242346707</v>
+        <v>61.10487004692538</v>
       </c>
     </row>
     <row r="39">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7.979351009583292</v>
+        <v>24.50178569079909</v>
       </c>
       <c r="F41" t="n">
-        <v>206.543823621494</v>
+        <v>504.3234652874118</v>
       </c>
     </row>
     <row r="42">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7.979351009583292</v>
+        <v>24.50178569079909</v>
       </c>
       <c r="F42" t="n">
-        <v>206.543823621494</v>
+        <v>504.3234652874118</v>
       </c>
     </row>
     <row r="43">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5.960068763988501</v>
+        <v>22.48233608801895</v>
       </c>
       <c r="F43" t="n">
-        <v>119.3035611957149</v>
+        <v>417.0759724287396</v>
       </c>
     </row>
     <row r="44">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.019282245594792</v>
+        <v>2.019449602780145</v>
       </c>
       <c r="F44" t="n">
-        <v>87.24026242577914</v>
+        <v>87.24749285867227</v>
       </c>
     </row>
     <row r="45">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12.17645308772521</v>
+        <v>12.17689268818927</v>
       </c>
       <c r="F45" t="n">
-        <v>322.8109175575095</v>
+        <v>322.8247017687741</v>
       </c>
     </row>
     <row r="46">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>18.13652185171371</v>
+        <v>34.65922877620822</v>
       </c>
       <c r="F46" t="n">
-        <v>442.1144787532244</v>
+        <v>739.9006741975136</v>
       </c>
     </row>
     <row r="47">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>18.13652185171371</v>
+        <v>34.65922877620822</v>
       </c>
       <c r="F47" t="n">
-        <v>442.1144787532244</v>
+        <v>739.9006741975136</v>
       </c>
     </row>
     <row r="48">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12.42088951864316</v>
+        <v>28.93717517244981</v>
       </c>
       <c r="F48" t="n">
-        <v>223.7623246783565</v>
+        <v>521.3032107316833</v>
       </c>
     </row>
     <row r="49">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.715632333070551</v>
+        <v>5.722053603758406</v>
       </c>
       <c r="F49" t="n">
-        <v>218.3521540748678</v>
+        <v>218.5974634658303</v>
       </c>
     </row>
     <row r="50">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.02690850495147</v>
+        <v>11.02728293652756</v>
       </c>
       <c r="F50" t="n">
-        <v>198.6497567167007</v>
+        <v>198.6565021015439</v>
       </c>
     </row>
     <row r="51">
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4.928623781734792</v>
+        <v>4.928791138920144</v>
       </c>
       <c r="F53" t="n">
-        <v>178.7495869981341</v>
+        <v>178.7568174310272</v>
       </c>
     </row>
     <row r="54">
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.928623781734792</v>
+        <v>4.928791138920144</v>
       </c>
       <c r="F54" t="n">
-        <v>178.7495869981341</v>
+        <v>178.7568174310272</v>
       </c>
     </row>
     <row r="55">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.860347289067589</v>
+        <v>1.860352828590425</v>
       </c>
       <c r="F55" t="n">
-        <v>54.58842615732538</v>
+        <v>54.58861776379706</v>
       </c>
     </row>
     <row r="56">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.860347289067589</v>
+        <v>1.860352828590425</v>
       </c>
       <c r="F56" t="n">
-        <v>54.58842615732538</v>
+        <v>54.58861776379706</v>
       </c>
     </row>
     <row r="57">
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.09981176121597812</v>
+        <v>0.09981703039135524</v>
       </c>
       <c r="F57" t="n">
-        <v>1.699894105269323</v>
+        <v>1.699983844595171</v>
       </c>
     </row>
     <row r="58">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.09981176121597812</v>
+        <v>0.09981703039135524</v>
       </c>
       <c r="F58" t="n">
-        <v>1.699894105269323</v>
+        <v>1.699983844595171</v>
       </c>
     </row>
     <row r="59">
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.990903011398164</v>
+        <v>1.990915593225673</v>
       </c>
       <c r="F59" t="n">
-        <v>56.2883202625947</v>
+        <v>56.28860160839222</v>
       </c>
     </row>
     <row r="60">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.990903011398164</v>
+        <v>1.990915593225673</v>
       </c>
       <c r="F60" t="n">
-        <v>56.2883202625947</v>
+        <v>56.28860160839222</v>
       </c>
     </row>
     <row r="61">
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.1301892537599715</v>
+        <v>0.1301961265974199</v>
       </c>
       <c r="F61" t="n">
-        <v>2.345359406485886</v>
+        <v>2.34548322065252</v>
       </c>
     </row>
     <row r="62">
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1236797910719729</v>
+        <v>0.1236863202675489</v>
       </c>
       <c r="F62" t="n">
-        <v>2.228091436161592</v>
+        <v>2.228209059619894</v>
       </c>
     </row>
     <row r="63">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.860713757638193</v>
+        <v>1.860719466628253</v>
       </c>
       <c r="F63" t="n">
-        <v>53.94296085610881</v>
+        <v>53.9431183877397</v>
       </c>
     </row>
     <row r="64">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>12.59703213921056</v>
+        <v>12.59707078907327</v>
       </c>
       <c r="F64" t="n">
-        <v>226.9355339878783</v>
+        <v>226.936230265155</v>
       </c>
     </row>
     <row r="65">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>12.59703213921056</v>
+        <v>12.59707078907327</v>
       </c>
       <c r="F65" t="n">
-        <v>226.9355339878783</v>
+        <v>226.936230265155</v>
       </c>
     </row>
     <row r="66">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12.6099208753328</v>
+        <v>12.60996020560641</v>
       </c>
       <c r="F66" t="n">
-        <v>227.1550420527761</v>
+        <v>227.1557499181309</v>
       </c>
     </row>
     <row r="67">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.847825021515956</v>
+        <v>1.847830050095108</v>
       </c>
       <c r="F67" t="n">
-        <v>53.723452791211</v>
+        <v>53.72359873476372</v>
       </c>
     </row>
     <row r="68">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1.847825021515956</v>
+        <v>1.847830050095108</v>
       </c>
       <c r="F68" t="n">
-        <v>53.723452791211</v>
+        <v>53.72359873476372</v>
       </c>
     </row>
     <row r="69">
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="F70" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
     <row r="71">
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="F71" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
     <row r="72">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1.847283111895956</v>
+        <v>1.847288140475108</v>
       </c>
       <c r="F72" t="n">
-        <v>53.58364010925099</v>
+        <v>53.58378605280372</v>
       </c>
     </row>
     <row r="73">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="F78" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
     <row r="79">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="F79" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
     <row r="80">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>9.46558910365119</v>
+        <v>9.465305211085866</v>
       </c>
       <c r="F80" t="n">
-        <v>199.863228421068</v>
+        <v>199.8100441811412</v>
       </c>
     </row>
     <row r="81">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.002123047241076949</v>
+        <v>0.002123048468099186</v>
       </c>
       <c r="F81" t="n">
-        <v>0.565405695149131</v>
+        <v>0.5654060219272392</v>
       </c>
     </row>
     <row r="82">
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="F82" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
     <row r="83">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="F83" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
     <row r="84">
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.891269580504547</v>
+        <v>0.8911852099701643</v>
       </c>
       <c r="F84" t="n">
-        <v>20.94916414365624</v>
+        <v>20.94604927740552</v>
       </c>
     </row>
     <row r="85">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.0001482059276655101</v>
+        <v>0.0001482080801861594</v>
       </c>
       <c r="F85" t="n">
-        <v>0.03946990624402331</v>
+        <v>0.03947047949901761</v>
       </c>
     </row>
     <row r="86">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6.297378731066566</v>
+        <v>22.82011869798682</v>
       </c>
       <c r="F86" t="n">
-        <v>417.2474020723294</v>
+        <v>715.1093689792642</v>
       </c>
     </row>
     <row r="87">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6.297378731066566</v>
+        <v>22.82011869798682</v>
       </c>
       <c r="F87" t="n">
-        <v>417.2474020723294</v>
+        <v>715.1093689792642</v>
       </c>
     </row>
     <row r="88">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.001066165429740137</v>
+        <v>0.004275750622102236</v>
       </c>
       <c r="F88" t="n">
-        <v>0.283939044917534</v>
+        <v>1.138709354177023</v>
       </c>
     </row>
     <row r="89">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.046065991715117</v>
+        <v>2.05248726240297</v>
       </c>
       <c r="F89" t="n">
-        <v>78.16509016602832</v>
+        <v>78.41039955699071</v>
       </c>
     </row>
     <row r="90">
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>10.28358489969196</v>
+        <v>10.28359142888755</v>
       </c>
       <c r="F90" t="n">
-        <v>522.6522343125655</v>
+        <v>522.6523519360239</v>
       </c>
     </row>
     <row r="91">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.006509462687998574</v>
+        <v>0.006509806329870996</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1172679703242943</v>
+        <v>0.117274161032626</v>
       </c>
     </row>
     <row r="92">
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.003337418598482597</v>
+        <v>0.006547007170387581</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8888146463106883</v>
+        <v>1.74358585560328</v>
       </c>
     </row>
     <row r="93">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>7.999294779828134</v>
+        <v>7.998165999562447</v>
       </c>
       <c r="F93" t="n">
-        <v>1527.924897546044</v>
+        <v>1527.552435021102</v>
       </c>
     </row>
     <row r="94">
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7.999356919261684</v>
+        <v>7.99829927330985</v>
       </c>
       <c r="F95" t="n">
-        <v>1527.937875448637</v>
+        <v>1527.587930546114</v>
       </c>
     </row>
     <row r="96">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>8.815229668061383</v>
+        <v>8.81446244264343</v>
       </c>
       <c r="F96" t="n">
-        <v>1850.161475644985</v>
+        <v>1849.86483227907</v>
       </c>
     </row>
     <row r="97">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8815229668061383</v>
+        <v>0.881446244264343</v>
       </c>
       <c r="F97" t="n">
-        <v>16.46453005862058</v>
+        <v>16.46309708336851</v>
       </c>
     </row>
   </sheetData>
@@ -3197,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.718400825526719</v>
+        <v>1.718401916564142</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.277508476626917</v>
+        <v>6.277512462307424</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.8085214196575742</v>
+        <v>0.8077799138122509</v>
       </c>
       <c r="AF3" t="n">
         <v>7.0961411384608e-24</v>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0009041266240976428</v>
+        <v>0.0008809761736061324</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.718400825526719</v>
+        <v>1.718401916564142</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.277508476626917</v>
+        <v>6.277512462307424</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.8085214196575742</v>
+        <v>0.8077799138122509</v>
       </c>
       <c r="AF4" t="n">
         <v>7.0961411384608e-24</v>
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0009041266240976428</v>
+        <v>0.0008809761736061324</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -3442,13 +3442,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000989021154827144</v>
+        <v>0.003966024895881722</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>5.488078388135823</v>
+        <v>22.00747214724768</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.000989021154827144</v>
+        <v>0.003966024895881722</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>5.488078388135823</v>
+        <v>22.00747214724768</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000989021154827144</v>
+        <v>0.003966024895881722</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>5.488078388135823</v>
+        <v>22.00747214724768</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001071216271709918</v>
+        <v>0.004296004791410235</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0005933726960295194</v>
+        <v>0.0008804305618959973</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.717329609255009</v>
+        <v>1.714105911772732</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.277508476626917</v>
+        <v>6.277512462307424</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0008085214196576189</v>
+        <v>7.270019297010451e-08</v>
       </c>
       <c r="AF8" t="n">
         <v>7.0961411384608e-24</v>
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0003107539280681235</v>
+        <v>5.456117101351201e-07</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -3995,10 +3995,10 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.720667027853492</v>
+        <v>1.72065291894312</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.277508476626917</v>
+        <v>6.277512462307424</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0008085214196576189</v>
+        <v>7.270019297010451e-08</v>
       </c>
       <c r="AF9" t="n">
         <v>7.0961411384608e-24</v>
@@ -4040,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0003107539280681235</v>
+        <v>5.456117101351201e-07</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -4128,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0860333513926746</v>
+        <v>0.08603264594715598</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3138754238313459</v>
+        <v>0.3138756231153712</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>4.042607098288095e-05</v>
+        <v>3.635009648505226e-09</v>
       </c>
       <c r="AF10" t="n">
         <v>3.5480705692304e-25</v>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.553769640340617e-05</v>
+        <v>2.728058550675601e-08</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -4261,10 +4261,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.634633676460817</v>
+        <v>1.634620272995964</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.96363305279557</v>
+        <v>5.963636839192053</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0007680953486747378</v>
+        <v>6.906518332159928e-08</v>
       </c>
       <c r="AF11" t="n">
         <v>6.741334081537759e-24</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0002952162316647173</v>
+        <v>5.183311246283641e-07</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -4394,10 +4394,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.08615145506787986</v>
+        <v>0.08616595108274609</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.3138754255601163</v>
+        <v>0.3138756248396351</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4506,13 +4506,13 @@
         <v>0.006234</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4649769364799967</v>
+        <v>0.4649769364799985</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>8.963921865831969</v>
+        <v>8.963928395027548</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.00221244825986644</v>
+        <v>0.002212449664581673</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -4542,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0008352792180895346</v>
+        <v>0.0008106171907463337</v>
       </c>
       <c r="AF13" t="n">
         <v>0.000555375617156357</v>
@@ -4572,7 +4572,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.002304974844496024</v>
+        <v>0.002039214933240497</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -4639,13 +4639,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.007941648349604849</v>
+        <v>0.007940957155534622</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.869610494281731</v>
+        <v>0.8695348085310411</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4660,13 +4660,13 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0001718572682793962</v>
+        <v>0.0001718573773938914</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.003970824174802425</v>
+        <v>0.003970478577767311</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.002026369472825973</v>
+        <v>0.002024511062186041</v>
       </c>
       <c r="AF14" t="n">
         <v>0.007103244382843643</v>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0002260287628192135</v>
+        <v>0.0002202412242777775</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -4772,13 +4772,13 @@
         <v>0.006234000000000003</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2036621057748839</v>
+        <v>0.2035915489071721</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>8.766250726263989</v>
+        <v>8.766137904851128</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.940101878949082e-05</v>
+        <v>8.940119648248612e-05</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0008352792180895338</v>
+        <v>0.0008106171907463332</v>
       </c>
       <c r="AF15" t="n">
         <v>0.0005553756171563567</v>
@@ -4838,7 +4838,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.002304974844496023</v>
+        <v>0.002039214933240496</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -4905,13 +4905,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.936402999999997</v>
+        <v>2.936402999999999</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>6.695613791071969</v>
+        <v>6.695620320267547</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -5038,13 +5038,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2613148307051129</v>
+        <v>0.2613853875728264</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.19767113956798</v>
+        <v>0.1977904901764198</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.004952864901581989</v>
+        <v>0.004951508560121844</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8604849911895133</v>
+        <v>0.8604056165107233</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -5192,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.365134061388612e-05</v>
+        <v>2.3649297207732e-05</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -5201,13 +5201,13 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.003970824174802425</v>
+        <v>0.003970478577767311</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.001985412087401212</v>
+        <v>0.001985239288883655</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.002026369472825973</v>
+        <v>0.002024511062186041</v>
       </c>
       <c r="AF18" t="n">
         <v>0.007103244382843643</v>
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.0002260287628192135</v>
+        <v>0.0002202412242777775</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -5304,13 +5304,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.00298878344802286</v>
+        <v>0.002989448595412778</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.009125503092217713</v>
+        <v>0.009129192020317811</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5437,13 +5437,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2643036141531357</v>
+        <v>0.2643748361682391</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2067966426601977</v>
+        <v>0.2069196821967376</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5570,13 +5570,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2643036141531357</v>
+        <v>0.2643748361682391</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2067966426601977</v>
+        <v>0.2069196821967376</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5703,13 +5703,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2643036141531357</v>
+        <v>0.2643748361682391</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2067966426601977</v>
+        <v>0.2069196821967376</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5836,13 +5836,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>9.890211548271438e-05</v>
+        <v>0.0003966024895881721</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5488078388135822</v>
+        <v>2.200747214724767</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5857,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.050841969780978e-06</v>
+        <v>2.025416930799929e-05</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -5872,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.0005933726960295194</v>
+        <v>0.0008804305618959973</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -5969,13 +5969,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>9.890211548271438e-05</v>
+        <v>0.0003966024895881721</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5488078388135822</v>
+        <v>2.200747214724767</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5990,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.050841969780978e-06</v>
+        <v>2.025416930799929e-05</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -6035,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.0005933726960295194</v>
+        <v>0.0008804305618959973</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -6102,13 +6102,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0008901190393444296</v>
+        <v>0.00356942240629355</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.939270549322241</v>
+        <v>19.80672493252291</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -6304,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="AQ26" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="AQ27" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.2692376327459722</v>
+        <v>0.2692599470373526</v>
       </c>
     </row>
     <row r="29">
@@ -6652,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1346188163729861</v>
+        <v>0.1346299735186763</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -6770,10 +6770,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.615425796475833</v>
+        <v>1.615559682224116</v>
       </c>
       <c r="U30" t="n">
-        <v>0.5488078388135822</v>
+        <v>2.200747214724767</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.4038564491189583</v>
+        <v>0.403889920556029</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6903,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.615425796475833</v>
+        <v>1.615559682224116</v>
       </c>
       <c r="U31" t="n">
-        <v>0.5488078388135822</v>
+        <v>2.200747214724767</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6918,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4038564491189583</v>
+        <v>0.403889920556029</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -7166,13 +7166,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.290074883251738</v>
+        <v>1.290074883251739</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.280493666744167</v>
+        <v>1.280493666744168</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -7299,13 +7299,13 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.646328116748258</v>
+        <v>1.646328116748259</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.023238224607176</v>
+        <v>2.023238224607177</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7432,13 +7432,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.936402999999997</v>
+        <v>2.936402999999999</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>6.695613791071969</v>
+        <v>6.695620320267547</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7565,13 +7565,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.936402999999997</v>
+        <v>2.936402999999999</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>6.695613791071969</v>
+        <v>6.695620320267547</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.268202108648652</v>
+        <v>3.268202108648653</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7837,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.391881899720625</v>
+        <v>3.391888428916202</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.2651937331924801</v>
+        <v>0.2679442585745327</v>
       </c>
       <c r="T41" t="n">
-        <v>1.615425796475833</v>
+        <v>1.615559682224116</v>
       </c>
       <c r="U41" t="n">
-        <v>5.694875030796021</v>
+        <v>22.21439182944441</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8248,7 +8248,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.4038564491189583</v>
+        <v>0.403889920556029</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -8363,13 +8363,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.2651937331924801</v>
+        <v>0.2679442585745327</v>
       </c>
       <c r="T42" t="n">
-        <v>1.615425796475833</v>
+        <v>1.615559682224116</v>
       </c>
       <c r="U42" t="n">
-        <v>5.694875030796021</v>
+        <v>22.21439182944441</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8381,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.4038564491189583</v>
+        <v>0.403889920556029</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -8496,13 +8496,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.2651937331924801</v>
+        <v>0.2679442585745327</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>5.694875030796021</v>
+        <v>22.21439182944441</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.615425796475833</v>
+        <v>1.615559682224116</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.4038564491189583</v>
+        <v>0.403889920556029</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -8762,13 +8762,13 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.299089165547477</v>
+        <v>2.29921950332343</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>9.877363922177731</v>
+        <v>9.877673184865841</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -8895,13 +8895,13 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.564282898739958</v>
+        <v>2.567163761897963</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>15.57223895297375</v>
+        <v>32.09206501431025</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -9028,13 +9028,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.564282898739958</v>
+        <v>2.567163761897963</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>15.57223895297375</v>
+        <v>32.09206501431025</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -9167,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>12.42088951864316</v>
+        <v>28.93717517244981</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -9294,13 +9294,13 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.564282898739958</v>
+        <v>2.567163761897963</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>3.151349434330593</v>
+        <v>3.154889841860443</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>11.02690850495147</v>
+        <v>11.02728293652756</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>1.929554640486633</v>
+        <v>1.929688526234916</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
         <v>1.68713681538</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.8523358557389582</v>
+        <v>0.8523693271760289</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -9962,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1.929554640486633</v>
+        <v>1.929688526234916</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1.68713681538</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.8523358557389582</v>
+        <v>0.8523693271760289</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.0192955464048663</v>
+        <v>0.01929688526234918</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -10104,13 +10104,13 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.05397805804348943</v>
+        <v>0.05398026715833626</v>
       </c>
       <c r="X55" t="n">
         <v>1.68713681538</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.08314852861923372</v>
+        <v>0.08315052016973956</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -10228,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.0192955464048663</v>
+        <v>0.01929688526234918</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -10237,13 +10237,13 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.05397805804348943</v>
+        <v>0.05398026715833626</v>
       </c>
       <c r="X56" t="n">
         <v>1.68713681538</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.08314852861923372</v>
+        <v>0.08315052016973956</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>0.09981176121597812</v>
+        <v>0.09981703039135524</v>
       </c>
       <c r="W57" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0.09981176121597812</v>
+        <v>0.09981703039135524</v>
       </c>
       <c r="W58" t="n">
         <v>0</v>
@@ -10627,22 +10627,22 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.001204042095663656</v>
+        <v>0.00120412564037059</v>
       </c>
       <c r="U59" t="n">
-        <v>0.1301892537599715</v>
+        <v>0.1301961265974199</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01301892537599714</v>
+        <v>0.01301961265974198</v>
       </c>
       <c r="W59" t="n">
-        <v>0.003368230821913738</v>
+        <v>0.003368368670680182</v>
       </c>
       <c r="X59" t="n">
-        <v>1.76488389906538</v>
+        <v>1.764887853300624</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.06145031965923847</v>
+        <v>0.06145116573683625</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -10760,22 +10760,22 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.001204042095663656</v>
+        <v>0.00120412564037059</v>
       </c>
       <c r="U60" t="n">
-        <v>0.1301892537599715</v>
+        <v>0.1301961265974199</v>
       </c>
       <c r="V60" t="n">
-        <v>0.01301892537599714</v>
+        <v>0.01301961265974198</v>
       </c>
       <c r="W60" t="n">
-        <v>0.003368230821913738</v>
+        <v>0.003368368670680182</v>
       </c>
       <c r="X60" t="n">
-        <v>1.76488389906538</v>
+        <v>1.764887853300624</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.06145031965923847</v>
+        <v>0.06145116573683625</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>0.1301892537599715</v>
+        <v>0.1301961265974199</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -11029,7 +11029,7 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0.1236797910719729</v>
+        <v>0.1236863202675489</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -11159,22 +11159,22 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.001204042095663656</v>
+        <v>0.00120412564037059</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.01301892537599714</v>
+        <v>0.01301961265974198</v>
       </c>
       <c r="W63" t="n">
-        <v>0.003368230821913738</v>
+        <v>0.003368368670680182</v>
       </c>
       <c r="X63" t="n">
-        <v>1.76488389906538</v>
+        <v>1.764887853300624</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.06145031965923847</v>
+        <v>0.06145116573683625</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -11295,7 +11295,7 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>12.59703213921056</v>
+        <v>12.59707078907327</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>12.59703213921056</v>
+        <v>12.59707078907327</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -11561,10 +11561,10 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>12.59703213921056</v>
+        <v>12.59707078907327</v>
       </c>
       <c r="V66" t="n">
-        <v>0.01288873612223717</v>
+        <v>0.01288941653314456</v>
       </c>
       <c r="W66" t="n">
         <v>0</v>
@@ -11691,22 +11691,22 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.001204042095663656</v>
+        <v>0.00120412564037059</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0001301892537599707</v>
+        <v>0.0001301961265974191</v>
       </c>
       <c r="W67" t="n">
-        <v>0.003368230821913738</v>
+        <v>0.003368368670680182</v>
       </c>
       <c r="X67" t="n">
-        <v>1.76488389906538</v>
+        <v>1.764887853300624</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.06145031965923847</v>
+        <v>0.06145116573683625</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -11824,22 +11824,22 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.001204042095663656</v>
+        <v>0.00120412564037059</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0.0001301892537599707</v>
+        <v>0.0001301961265974191</v>
       </c>
       <c r="W68" t="n">
-        <v>0.003368230821913738</v>
+        <v>0.003368368670680182</v>
       </c>
       <c r="X68" t="n">
-        <v>1.76488389906538</v>
+        <v>1.764887853300624</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.06145031965923847</v>
+        <v>0.06145116573683625</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -12087,13 +12087,13 @@
         <v>0.006234</v>
       </c>
       <c r="S70" t="n">
-        <v>0.4649769364799967</v>
+        <v>0.4649769364799985</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>8.963921865831969</v>
+        <v>8.963928395027548</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -12220,13 +12220,13 @@
         <v>0.006234</v>
       </c>
       <c r="S71" t="n">
-        <v>0.4649769364799967</v>
+        <v>0.4649769364799985</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>8.963921865831969</v>
+        <v>8.963928395027548</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -12356,22 +12356,22 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0.001204042095663656</v>
+        <v>0.00120412564037059</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>0.0001301892537599707</v>
+        <v>0.0001301961265974191</v>
       </c>
       <c r="W72" t="n">
-        <v>0.003368230821913738</v>
+        <v>0.003368368670680182</v>
       </c>
       <c r="X72" t="n">
-        <v>1.76488389906538</v>
+        <v>1.764887853300624</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.06145031965923847</v>
+        <v>0.06145116573683625</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -13151,13 +13151,13 @@
         <v>0.006234</v>
       </c>
       <c r="S78" t="n">
-        <v>0.4649769364799967</v>
+        <v>0.4649769364799985</v>
       </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>8.963921865831969</v>
+        <v>8.963928395027548</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>8.94010187894908e-05</v>
+        <v>8.94011964824862e-05</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.0008352792180895346</v>
+        <v>0.0008106171907463337</v>
       </c>
       <c r="AF78" t="n">
         <v>0.000555375617156357</v>
@@ -13217,7 +13217,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO78" t="n">
-        <v>0.002304974844496024</v>
+        <v>0.002039214933240497</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -13284,13 +13284,13 @@
         <v>0.006234</v>
       </c>
       <c r="S79" t="n">
-        <v>0.4649769364799967</v>
+        <v>0.4649769364799985</v>
       </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>8.963921865831969</v>
+        <v>8.963928395027548</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -13305,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>8.94010187894908e-05</v>
+        <v>8.94011964824862e-05</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -13320,7 +13320,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0.0008352792180895346</v>
+        <v>0.0008106171907463337</v>
       </c>
       <c r="AF79" t="n">
         <v>0.000555375617156357</v>
@@ -13350,7 +13350,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO79" t="n">
-        <v>0.002304974844496024</v>
+        <v>0.002039214933240497</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -13417,13 +13417,13 @@
         <v>0.006234</v>
       </c>
       <c r="S80" t="n">
-        <v>0.4649769364799967</v>
+        <v>0.4649769364799985</v>
       </c>
       <c r="T80" t="n">
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>8.963921865831969</v>
+        <v>8.963928395027548</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -13438,7 +13438,7 @@
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>8.94010187894908e-05</v>
+        <v>8.94011964824862e-05</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -13453,7 +13453,7 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0.0008352792180895346</v>
+        <v>0.0008106171907463337</v>
       </c>
       <c r="AF80" t="n">
         <v>0.000555375617156357</v>
@@ -13483,7 +13483,7 @@
         <v>0.002094222</v>
       </c>
       <c r="AO80" t="n">
-        <v>0.002304974844496024</v>
+        <v>0.002039214933240497</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -13571,7 +13571,7 @@
         <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>0.002123047241076949</v>
+        <v>0.002123048468099186</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -13683,13 +13683,13 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.007941648349604849</v>
+        <v>0.007940957155534622</v>
       </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>0.869610494281731</v>
+        <v>0.8695348085310411</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -13704,13 +13704,13 @@
         <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.365134061388612e-05</v>
+        <v>2.3649297207732e-05</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.003970824174802425</v>
+        <v>0.003970478577767311</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -13719,7 +13719,7 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.002026369472825973</v>
+        <v>0.002024511062186041</v>
       </c>
       <c r="AF82" t="n">
         <v>0.007103244382843643</v>
@@ -13749,7 +13749,7 @@
         <v>0</v>
       </c>
       <c r="AO82" t="n">
-        <v>0.0002260287628192135</v>
+        <v>0.0002202412242777775</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -13816,13 +13816,13 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.007941648349604849</v>
+        <v>0.007940957155534622</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>0.869610494281731</v>
+        <v>0.8695348085310411</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -13837,13 +13837,13 @@
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.365134061388612e-05</v>
+        <v>2.3649297207732e-05</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.003970824174802425</v>
+        <v>0.003970478577767311</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13852,7 +13852,7 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0.002026369472825973</v>
+        <v>0.002024511062186041</v>
       </c>
       <c r="AF83" t="n">
         <v>0.007103244382843643</v>
@@ -13882,7 +13882,7 @@
         <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>0.0002260287628192135</v>
+        <v>0.0002202412242777775</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -13949,13 +13949,13 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.007941648349604849</v>
+        <v>0.007940957155534622</v>
       </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0.869610494281731</v>
+        <v>0.8695348085310411</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -13970,13 +13970,13 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.365134061388612e-05</v>
+        <v>2.3649297207732e-05</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.003970824174802425</v>
+        <v>0.003970478577767311</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13985,7 +13985,7 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.002026369472825973</v>
+        <v>0.002024511062186041</v>
       </c>
       <c r="AF84" t="n">
         <v>0.007103244382843643</v>
@@ -14015,7 +14015,7 @@
         <v>0</v>
       </c>
       <c r="AO84" t="n">
-        <v>0.0002260287628192135</v>
+        <v>0.0002202412242777775</v>
       </c>
       <c r="AP84" t="n">
         <v>0</v>
@@ -14103,7 +14103,7 @@
         <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>0.0001482059276655101</v>
+        <v>0.0001482080801861594</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -14215,13 +14215,13 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.000989021154827144</v>
+        <v>0.003966024895881722</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>5.488078388135823</v>
+        <v>22.00747214724768</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -14236,7 +14236,7 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>5.050841969780978e-06</v>
+        <v>2.025416930799929e-05</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -14251,7 +14251,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="AO86" t="n">
-        <v>0.0005933726960295194</v>
+        <v>0.0008804305618959973</v>
       </c>
       <c r="AP86" t="n">
         <v>0</v>
@@ -14348,13 +14348,13 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.000989021154827144</v>
+        <v>0.003966024895881722</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>5.488078388135823</v>
+        <v>22.00747214724768</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -14369,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>5.050841969780978e-06</v>
+        <v>2.025416930799929e-05</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -14384,7 +14384,7 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.8077128982379166</v>
+        <v>0.8077798411120579</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -14414,7 +14414,7 @@
         <v>0</v>
       </c>
       <c r="AO87" t="n">
-        <v>0.0005933726960295194</v>
+        <v>0.0008804305618959973</v>
       </c>
       <c r="AP87" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.001066165429740137</v>
+        <v>0.004275750622102236</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -14614,13 +14614,13 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.9179547819916993</v>
+        <v>0.9208356451497036</v>
       </c>
       <c r="T89" t="n">
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>1.128111209723417</v>
+        <v>1.131651617253266</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -14747,13 +14747,13 @@
         <v>0.006234</v>
       </c>
       <c r="S90" t="n">
-        <v>0.4649769364799967</v>
+        <v>0.4649769364799985</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>8.963921865831969</v>
+        <v>8.963928395027548</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -14886,7 +14886,7 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>0.006509462687998574</v>
+        <v>0.006509806329870996</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -15034,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.003337418598482597</v>
+        <v>0.006547007170387581</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -15167,10 +15167,10 @@
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.720667027853492</v>
+        <v>1.72065291894312</v>
       </c>
       <c r="AA93" t="n">
-        <v>6.277508476626917</v>
+        <v>6.277512462307424</v>
       </c>
       <c r="AB93" t="n">
         <v>0</v>
@@ -15182,7 +15182,7 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0.0008085214196576189</v>
+        <v>7.270019297010451e-08</v>
       </c>
       <c r="AF93" t="n">
         <v>7.0961411384608e-24</v>
@@ -15212,7 +15212,7 @@
         <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>0.0003107539280681235</v>
+        <v>5.456117101351201e-07</v>
       </c>
       <c r="AP93" t="n">
         <v>0</v>
@@ -15433,10 +15433,10 @@
         <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.720785131054865</v>
+        <v>1.720786223606118</v>
       </c>
       <c r="AA95" t="n">
-        <v>6.277508476626917</v>
+        <v>6.277512462307424</v>
       </c>
       <c r="AB95" t="n">
         <v>0</v>
@@ -15448,10 +15448,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0.0007680953484896853</v>
+        <v>6.90651833054091e-08</v>
       </c>
       <c r="AF95" t="n">
-        <v>6.741334079745978e-24</v>
+        <v>6.741334079717528e-24</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>0.0002952162314128801</v>
+        <v>5.183311244066502e-07</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -15566,10 +15566,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.718572682794999</v>
+        <v>1.718573773941536</v>
       </c>
       <c r="AA96" t="n">
-        <v>6.277508476626917</v>
+        <v>6.277512462307424</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>
@@ -15581,7 +15581,7 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0.8105477891304002</v>
+        <v>0.8098044248744369</v>
       </c>
       <c r="AF96" t="n">
         <v>0.007103244382843643</v>
@@ -15611,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="AO96" t="n">
-        <v>0.001130155386916856</v>
+        <v>0.00110121739788391</v>
       </c>
       <c r="AP96" t="n">
         <v>0</v>
@@ -15678,13 +15678,13 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0.007941648349604849</v>
+        <v>0.007940957155534622</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>0.869610494281731</v>
+        <v>0.8695348085310411</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -15705,7 +15705,7 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0.003970824174802425</v>
+        <v>0.003970478577767311</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -16196,10 +16196,10 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1951545120208661</v>
+        <v>0.1951714721143091</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7129210398787297</v>
+        <v>0.7129829969778954</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -16211,10 +16211,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.09182176868620129</v>
+        <v>0.09174547200129475</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.058911172153517e-25</v>
+        <v>8.059606422538621e-25</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -16241,7 +16241,7 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0001026794142028914</v>
+        <v>0.0001000589065008308</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -16329,10 +16329,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1951545120208661</v>
+        <v>0.1951714721143091</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7129210398787297</v>
+        <v>0.7129829969778954</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -16344,10 +16344,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.09182176868620129</v>
+        <v>0.09174547200129475</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.058911172153517e-25</v>
+        <v>8.059606422538621e-25</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -16374,7 +16374,7 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0001026794142028914</v>
+        <v>0.0001000589065008308</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -16707,13 +16707,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001570262455383735</v>
+        <v>0.0001737625462446141</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8713386364924344</v>
+        <v>0.9642083691113639</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001700763107899561</v>
+        <v>0.0001882198803163456</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -16743,7 +16743,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1282400515541909</v>
+        <v>0.03539107435821982</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -16773,7 +16773,7 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>9.420939704649958e-05</v>
+        <v>3.857410385534486e-05</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -16861,10 +16861,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.214774733239812</v>
+        <v>0.2144879421059167</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7850852866055723</v>
+        <v>0.7855119805240406</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -16876,10 +16876,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0001011162745286677</v>
+        <v>9.097054431563162e-09</v>
       </c>
       <c r="AF8" t="n">
-        <v>8.874661054182419e-25</v>
+        <v>8.879478795493449e-25</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -16906,7 +16906,7 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>3.88638800870662e-05</v>
+        <v>6.827298832120712e-08</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2151023402953605</v>
+        <v>0.2151309336461947</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7847577379517184</v>
+        <v>0.7848689890470948</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -17009,10 +17009,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0001010740873928627</v>
+        <v>9.089607914374582e-09</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.870958420428733e-25</v>
+        <v>8.872210377790366e-25</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -17039,7 +17039,7 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>3.884766552818548e-05</v>
+        <v>6.821710254137869e-08</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -17127,10 +17127,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2151023402953604</v>
+        <v>0.2151309336461948</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7847577379517184</v>
+        <v>0.7848689890470948</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -17142,10 +17142,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001010740873928626</v>
+        <v>9.089607914374582e-09</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.870958420428733e-25</v>
+        <v>8.872210377790368e-25</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -17172,7 +17172,7 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>3.884766552818548e-05</v>
+        <v>6.821710254137871e-08</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -17260,10 +17260,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.2151023402953605</v>
+        <v>0.2151309336461948</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.7847577379517184</v>
+        <v>0.7848689890470948</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -17275,10 +17275,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0001010740873928627</v>
+        <v>9.089607914374582e-09</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.870958420428733e-25</v>
+        <v>8.872210377790366e-25</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -17305,7 +17305,7 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>3.884766552818548e-05</v>
+        <v>6.821710254137871e-08</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -17393,10 +17393,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2153641648597014</v>
+        <v>0.2153924898532661</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.7846358351402987</v>
+        <v>0.7846075101467338</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -17499,19 +17499,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.168115361318599e-06</v>
+        <v>1.168150388553464e-06</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0006584484087227438</v>
+        <v>0.0006584681530286768</v>
       </c>
       <c r="S13" t="n">
-        <v>0.04911185818383544</v>
+        <v>0.04911333085738161</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9467885929534919</v>
+        <v>0.9468176731079725</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -17526,7 +17526,7 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.000233683515574344</v>
+        <v>0.0002336906712072521</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -17541,37 +17541,37 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>8.822397689929929e-05</v>
+        <v>8.562168822650512e-05</v>
       </c>
       <c r="AF13" t="n">
-        <v>5.865996011549809e-05</v>
+        <v>5.866171909947192e-05</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.828935662199605e-06</v>
+        <v>3.829050477082762e-06</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.399279518332941e-05</v>
+        <v>3.399381449500019e-05</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.001326037357273987</v>
+        <v>0.001326077119975079</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0002672149258109386</v>
+        <v>0.0002672229385469027</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.870164134272584e-05</v>
+        <v>3.87028018543721e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.244238065264536e-05</v>
+        <v>2.24430536123239e-05</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0009024942735711217</v>
+        <v>0.0009025213358630251</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0002211962052313382</v>
+        <v>0.0002212028380449185</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0002434563712711519</v>
+        <v>0.0002153926998266548</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -17638,13 +17638,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.008909008178297964</v>
+        <v>0.008909075991904575</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9755363955236271</v>
+        <v>0.9755438211135511</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -17659,13 +17659,13 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.000192790934727961</v>
+        <v>0.0001928093056017152</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.004454504089148982</v>
+        <v>0.004454537995952287</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -17674,13 +17674,13 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.002273198385390381</v>
+        <v>0.002271328574905601</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.00796847952885648</v>
+        <v>0.007969233778287878</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0004120623852213663</v>
+        <v>0.0004121013886245411</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -17704,7 +17704,7 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0002535609747297787</v>
+        <v>0.0002470918511722807</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -17765,19 +17765,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.227919098490573e-06</v>
+        <v>1.227983697620595e-06</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0006921588425382104</v>
+        <v>0.0006921952560601759</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02261253246744276</v>
+        <v>0.02260588776507664</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9733137561903473</v>
+        <v>0.9733524337034388</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -17792,7 +17792,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.926163889488407e-06</v>
+        <v>9.926705821507948e-06</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -17807,37 +17807,37 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>9.274075983142008e-05</v>
+        <v>9.0007278459326e-05</v>
       </c>
       <c r="AF15" t="n">
-        <v>6.166316078679627e-05</v>
+        <v>6.166640480062919e-05</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.024964812721267e-06</v>
+        <v>4.025176560568164e-06</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.573311660722526e-05</v>
+        <v>3.573499647720093e-05</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.001393926191049031</v>
+        <v>0.001393999523583208</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0002808954677512374</v>
+        <v>0.0002809102452743381</v>
       </c>
       <c r="AK15" t="n">
-        <v>4.068304049526476e-05</v>
+        <v>4.068518077390841e-05</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.359135812397076e-05</v>
+        <v>2.359259923278054e-05</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0009486990681685778</v>
+        <v>0.0009487489779179508</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0002325207371732523</v>
+        <v>0.0002325329697685038</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0002559205518841928</v>
+        <v>0.0002264252330568077</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -17904,13 +17904,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3048585840009939</v>
+        <v>0.3048583773485335</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.695141415999006</v>
+        <v>0.6951416226514665</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -18037,13 +18037,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5693307587367707</v>
+        <v>0.5692489528284143</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4306692412632293</v>
+        <v>0.4307510471715857</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -18170,13 +18170,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005620969349804777</v>
+        <v>0.005619997043926846</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9765579836224452</v>
+        <v>0.9765664267072036</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -18191,7 +18191,7 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.68417296482251e-05</v>
+        <v>2.684211867648083e-05</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -18200,19 +18200,19 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.00450645867059671</v>
+        <v>0.004506521113532733</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.002253229335298355</v>
+        <v>0.002253260556766367</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.002299711565824608</v>
+        <v>0.002297834295696495</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.008061418947119675</v>
+        <v>0.008062232337711825</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.0004168684261018044</v>
+        <v>0.0004169104877857561</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -18236,7 +18236,7 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.0002565183531606693</v>
+        <v>0.0002499753386999054</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -18303,13 +18303,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2467155979920801</v>
+        <v>0.2466818424776396</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7532844020079199</v>
+        <v>0.7533181575223605</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -18436,13 +18436,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5610347486137375</v>
+        <v>0.5609546172644082</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4389652513862625</v>
+        <v>0.4390453827355918</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -18569,13 +18569,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5610347486137375</v>
+        <v>0.5609546172644082</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4389652513862625</v>
+        <v>0.4390453827355918</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -18702,13 +18702,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5610347486137375</v>
+        <v>0.5609546172644082</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4389652513862625</v>
+        <v>0.4390453827355918</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -18835,13 +18835,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>7.2871204856793e-05</v>
+        <v>0.0001317693142136235</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4043623157503444</v>
+        <v>0.7311879245713969</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -18856,7 +18856,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.721466806678421e-06</v>
+        <v>6.729352613124097e-06</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.5951238938185938</v>
+        <v>0.2683810578432134</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -18901,7 +18901,7 @@
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.0004371977593983003</v>
+        <v>0.0002925189185630635</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -18968,13 +18968,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>7.2871204856793e-05</v>
+        <v>0.0001317693142136235</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4043623157503444</v>
+        <v>0.7311879245713969</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -18989,7 +18989,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.721466806678421e-06</v>
+        <v>6.729352613124097e-06</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -19004,7 +19004,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.5951238938185938</v>
+        <v>0.2683810578432134</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -19034,7 +19034,7 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.0004371977593983003</v>
+        <v>0.0002925189185630635</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -19769,10 +19769,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.6290378231992545</v>
+        <v>0.3828161936720468</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2137027210009318</v>
+        <v>0.5214797579099415</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -19784,7 +19784,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1572594557998136</v>
+        <v>0.09570404841801169</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -19902,10 +19902,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.6290378231992545</v>
+        <v>0.3828161936720468</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2137027210009318</v>
+        <v>0.5214797579099415</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -19917,7 +19917,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1572594557998136</v>
+        <v>0.09570404841801169</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -20431,13 +20431,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.3048585840009939</v>
+        <v>0.3048583773485335</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0.695141415999006</v>
+        <v>0.6951416226514665</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -20564,13 +20564,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.3048585840009939</v>
+        <v>0.3048583773485335</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.695141415999006</v>
+        <v>0.6951416226514665</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -21229,13 +21229,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0332350002993952</v>
+        <v>0.01093570329754174</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2024507750737733</v>
+        <v>0.06593640572208542</v>
       </c>
       <c r="U41" t="n">
-        <v>0.7137015308583882</v>
+        <v>0.9066437895498515</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -21247,7 +21247,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.05061269376844333</v>
+        <v>0.01648410143052136</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -21362,13 +21362,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.0332350002993952</v>
+        <v>0.01093570329754174</v>
       </c>
       <c r="T42" t="n">
-        <v>0.2024507750737733</v>
+        <v>0.06593640572208542</v>
       </c>
       <c r="U42" t="n">
-        <v>0.7137015308583882</v>
+        <v>0.9066437895498515</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -21380,7 +21380,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.05061269376844333</v>
+        <v>0.01648410143052136</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -21495,13 +21495,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.04449507945190409</v>
+        <v>0.0119179900845501</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0.9555049205480959</v>
+        <v>0.9880820099154498</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -21631,7 +21631,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -21761,13 +21761,13 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.188814357430994</v>
+        <v>0.1888182447032248</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0.811185642569006</v>
+        <v>0.8111817552967753</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -21894,13 +21894,13 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1413877985925763</v>
+        <v>0.07406869259768957</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0.8586122014074237</v>
+        <v>0.9259313074023103</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -22027,13 +22027,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.1413877985925763</v>
+        <v>0.07406869259768957</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0.8586122014074237</v>
+        <v>0.9259313074023103</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -22299,7 +22299,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0.5513562193454851</v>
+        <v>0.5513562193454852</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -22807,16 +22807,16 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.002801548588709665</v>
+        <v>0.002801453462080595</v>
       </c>
       <c r="N53" t="n">
-        <v>0.0004947937006345483</v>
+        <v>0.0004947768999061882</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.0001099515085749266</v>
+        <v>0.0001099477751696185</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -22828,7 +22828,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0.3914996814399704</v>
+        <v>0.3915135520751025</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -22837,13 +22837,13 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.0898441733674667</v>
+        <v>0.08984112270706107</v>
       </c>
       <c r="X53" t="n">
-        <v>0.3423139785252906</v>
+        <v>0.3423023552484387</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.1729358728693531</v>
+        <v>0.1729367918322414</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -22940,16 +22940,16 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.002801548588709665</v>
+        <v>0.002801453462080595</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0004947937006345483</v>
+        <v>0.0004947768999061882</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0001099515085749266</v>
+        <v>0.0001099477751696185</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -22961,7 +22961,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0.3914996814399704</v>
+        <v>0.3915135520751025</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -22970,13 +22970,13 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.0898441733674667</v>
+        <v>0.08984112270706107</v>
       </c>
       <c r="X54" t="n">
-        <v>0.3423139785252906</v>
+        <v>0.3423023552484387</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.1729358728693531</v>
+        <v>0.1729367918322414</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -23073,16 +23073,16 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.007422151273120887</v>
+        <v>0.007422129172379654</v>
       </c>
       <c r="N55" t="n">
-        <v>0.001310858469453979</v>
+        <v>0.001310854566145793</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.0002912948690734011</v>
+        <v>0.0002912940016924643</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -23094,7 +23094,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.0103720130742563</v>
+        <v>0.01037270186912355</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -23103,13 +23103,13 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02901504378278927</v>
+        <v>0.02901614485636936</v>
       </c>
       <c r="X55" t="n">
-        <v>0.9068934737586535</v>
+        <v>0.9068907733262247</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.04469516477265273</v>
+        <v>0.04469610220806452</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -23206,16 +23206,16 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.007422151273120887</v>
+        <v>0.007422129172379654</v>
       </c>
       <c r="N56" t="n">
-        <v>0.001310858469453979</v>
+        <v>0.001310854566145793</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.0002912948690734011</v>
+        <v>0.0002912940016924643</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -23227,7 +23227,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.0103720130742563</v>
+        <v>0.01037270186912355</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -23236,13 +23236,13 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02901504378278927</v>
+        <v>0.02901614485636936</v>
       </c>
       <c r="X56" t="n">
-        <v>0.9068934737586535</v>
+        <v>0.9068907733262247</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.04469516477265273</v>
+        <v>0.04469610220806452</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -23605,16 +23605,16 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.006935435287881313</v>
+        <v>0.006935391458574442</v>
       </c>
       <c r="N59" t="n">
-        <v>0.001224897439020594</v>
+        <v>0.001224889698135774</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0.000272192877753211</v>
+        <v>0.0002721911575979976</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -23626,22 +23626,22 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.0006047718491410017</v>
+        <v>0.0006048099901712413</v>
       </c>
       <c r="U59" t="n">
-        <v>0.06539206230269481</v>
+        <v>0.06539510114865127</v>
       </c>
       <c r="V59" t="n">
-        <v>0.006539206230269477</v>
+        <v>0.006539510114865123</v>
       </c>
       <c r="W59" t="n">
-        <v>0.00169181060183756</v>
+        <v>0.001691869149119861</v>
       </c>
       <c r="X59" t="n">
-        <v>0.8864740717961662</v>
+        <v>0.8864704557570722</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.03086555161523583</v>
+        <v>0.03086578152581212</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -23738,16 +23738,16 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.006935435287881313</v>
+        <v>0.006935391458574442</v>
       </c>
       <c r="N60" t="n">
-        <v>0.001224897439020594</v>
+        <v>0.001224889698135774</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.000272192877753211</v>
+        <v>0.0002721911575979976</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -23759,22 +23759,22 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.0006047718491410017</v>
+        <v>0.0006048099901712413</v>
       </c>
       <c r="U60" t="n">
-        <v>0.06539206230269481</v>
+        <v>0.06539510114865127</v>
       </c>
       <c r="V60" t="n">
-        <v>0.006539206230269477</v>
+        <v>0.006539510114865123</v>
       </c>
       <c r="W60" t="n">
-        <v>0.00169181060183756</v>
+        <v>0.001691869149119861</v>
       </c>
       <c r="X60" t="n">
-        <v>0.8864740717961662</v>
+        <v>0.8864704557570722</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.03086555161523583</v>
+        <v>0.03086578152581212</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -24137,16 +24137,16 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.007420689476454583</v>
+        <v>0.007420666708571933</v>
       </c>
       <c r="N63" t="n">
-        <v>0.00131060029517672</v>
+        <v>0.001310596274041782</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0002912374983930075</v>
+        <v>0.0002912366048289785</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -24158,22 +24158,22 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.0006470861467655022</v>
+        <v>0.0006471290605415904</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.006996737312525749</v>
+        <v>0.006997085209913123</v>
       </c>
       <c r="W63" t="n">
-        <v>0.001810182145473595</v>
+        <v>0.00181025067512401</v>
       </c>
       <c r="X63" t="n">
-        <v>0.9484983339433949</v>
+        <v>0.9484975489070998</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.03302513318181593</v>
+        <v>0.03302548655987882</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -24560,10 +24560,10 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0.9989778892151933</v>
+        <v>0.998977838444929</v>
       </c>
       <c r="V66" t="n">
-        <v>0.001022110784806729</v>
+        <v>0.00102216155507088</v>
       </c>
       <c r="W66" t="n">
         <v>0</v>
@@ -24669,16 +24669,16 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.007472449414432162</v>
+        <v>0.007472429079335143</v>
       </c>
       <c r="N67" t="n">
-        <v>0.001319741843304692</v>
+        <v>0.001319738251834622</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0002932689046257299</v>
+        <v>0.000293268106540484</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -24690,22 +24690,22 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.0006515996274776387</v>
+        <v>0.0006516430665842964</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>7.04554014823132e-05</v>
+        <v>7.045892915894398e-05</v>
       </c>
       <c r="W67" t="n">
-        <v>0.001822808319345325</v>
+        <v>0.001822877959207781</v>
       </c>
       <c r="X67" t="n">
-        <v>0.9551141902048004</v>
+        <v>0.9551137309460818</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.03325548628453177</v>
+        <v>0.03325585366125707</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -24802,16 +24802,16 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.007472449414432162</v>
+        <v>0.007472429079335143</v>
       </c>
       <c r="N68" t="n">
-        <v>0.001319741843304692</v>
+        <v>0.001319738251834622</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0002932689046257299</v>
+        <v>0.000293268106540484</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -24823,22 +24823,22 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.0006515996274776387</v>
+        <v>0.0006516430665842964</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>7.04554014823132e-05</v>
+        <v>7.045892915894398e-05</v>
       </c>
       <c r="W68" t="n">
-        <v>0.001822808319345325</v>
+        <v>0.001822877959207781</v>
       </c>
       <c r="X68" t="n">
-        <v>0.9551141902048004</v>
+        <v>0.9551137309460818</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.03325548628453177</v>
+        <v>0.03325585366125707</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -25080,19 +25080,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.075440141533842e-06</v>
+        <v>1.075439458721902e-06</v>
       </c>
       <c r="R70" t="n">
-        <v>0.000606208832893161</v>
+        <v>0.0006062084480027208</v>
       </c>
       <c r="S70" t="n">
-        <v>0.04521545171411233</v>
+        <v>0.04521542300619177</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>0.871672860511948</v>
+        <v>0.871672941988638</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -25122,37 +25122,37 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0.07882610790953661</v>
+        <v>0.07882605786174163</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.0007447422348046552</v>
+        <v>0.0007447417619574265</v>
       </c>
       <c r="AG70" t="n">
-        <v>3.924419392036026e-05</v>
+        <v>3.924416900367436e-05</v>
       </c>
       <c r="AH70" t="n">
-        <v>3.129589565693577e-05</v>
+        <v>3.129587578673526e-05</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.001220833019074512</v>
+        <v>0.001220832243950606</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0002460147919891031</v>
+        <v>0.0002460146357908815</v>
       </c>
       <c r="AK70" t="n">
-        <v>3.563115426906969e-05</v>
+        <v>3.563113164635305e-05</v>
       </c>
       <c r="AL70" t="n">
-        <v>2.066186082699279e-05</v>
+        <v>2.066184770848927e-05</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.0008308927366618954</v>
+        <v>0.0008308922091165119</v>
       </c>
       <c r="AN70" t="n">
-        <v>0.0002036470764259194</v>
+        <v>0.0002036469471275511</v>
       </c>
       <c r="AO70" t="n">
-        <v>0.0003053326277389953</v>
+        <v>0.0003053324338790528</v>
       </c>
       <c r="AP70" t="n">
         <v>0</v>
@@ -25213,19 +25213,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.075440141533842e-06</v>
+        <v>1.075439458721902e-06</v>
       </c>
       <c r="R71" t="n">
-        <v>0.000606208832893161</v>
+        <v>0.0006062084480027208</v>
       </c>
       <c r="S71" t="n">
-        <v>0.04521545171411233</v>
+        <v>0.04521542300619177</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>0.871672860511948</v>
+        <v>0.871672941988638</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -25255,37 +25255,37 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0.07882610790953661</v>
+        <v>0.07882605786174163</v>
       </c>
       <c r="AF71" t="n">
-        <v>0.0007447422348046552</v>
+        <v>0.0007447417619574265</v>
       </c>
       <c r="AG71" t="n">
-        <v>3.924419392036026e-05</v>
+        <v>3.924416900367436e-05</v>
       </c>
       <c r="AH71" t="n">
-        <v>3.129589565693577e-05</v>
+        <v>3.129587578673526e-05</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.001220833019074512</v>
+        <v>0.001220832243950606</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.0002460147919891031</v>
+        <v>0.0002460146357908815</v>
       </c>
       <c r="AK71" t="n">
-        <v>3.563115426906969e-05</v>
+        <v>3.563113164635305e-05</v>
       </c>
       <c r="AL71" t="n">
-        <v>2.066186082699279e-05</v>
+        <v>2.066184770848927e-05</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0008308927366618954</v>
+        <v>0.0008308922091165119</v>
       </c>
       <c r="AN71" t="n">
-        <v>0.0002036470764259194</v>
+        <v>0.0002036469471275511</v>
       </c>
       <c r="AO71" t="n">
-        <v>0.0003053326277389953</v>
+        <v>0.0003053324338790528</v>
       </c>
       <c r="AP71" t="n">
         <v>0</v>
@@ -25334,10 +25334,10 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0.007474641494355681</v>
+        <v>0.007474621147326126</v>
       </c>
       <c r="N72" t="n">
-        <v>0.00132012899608934</v>
+        <v>0.001320125402511812</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -25355,22 +25355,22 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0.0006517907774449852</v>
+        <v>0.0006518342287743472</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>7.047606992214158e-05</v>
+        <v>7.04795985773685e-05</v>
       </c>
       <c r="W72" t="n">
-        <v>0.00182334304916411</v>
+        <v>0.001823412708000098</v>
       </c>
       <c r="X72" t="n">
-        <v>0.9553943776674244</v>
+        <v>0.9553939175112705</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.03326524194559926</v>
+        <v>0.03326560940353977</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -26144,19 +26144,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.168377359179266e-06</v>
+        <v>1.168412402280187e-06</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0006585960928301166</v>
+        <v>0.0006586158460794981</v>
       </c>
       <c r="S78" t="n">
-        <v>0.04912287353574642</v>
+        <v>0.04912434687635985</v>
       </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>0.9470009491933564</v>
+        <v>0.9470300423623846</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -26171,7 +26171,7 @@
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>9.444844669520451e-06</v>
+        <v>9.445146721500175e-06</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -26186,37 +26186,37 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>8.824376475071581e-05</v>
+        <v>8.564089299486405e-05</v>
       </c>
       <c r="AF78" t="n">
-        <v>5.867311702154178e-05</v>
+        <v>5.867487680227101e-05</v>
       </c>
       <c r="AG78" t="n">
-        <v>3.829794458329976e-06</v>
+        <v>3.829909325220075e-06</v>
       </c>
       <c r="AH78" t="n">
-        <v>3.400041946421042e-05</v>
+        <v>3.400143923759211e-05</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.001326334775630319</v>
+        <v>0.001326374556342461</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.0002672748597363188</v>
+        <v>0.0002672828761017593</v>
       </c>
       <c r="AK78" t="n">
-        <v>3.87103217758165e-05</v>
+        <v>3.871148281313208e-05</v>
       </c>
       <c r="AL78" t="n">
-        <v>2.244741427853024e-05</v>
+        <v>2.24480875430349e-05</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.0009026966949900754</v>
+        <v>0.0009027237695402073</v>
       </c>
       <c r="AN78" t="n">
-        <v>0.0002212458175679937</v>
+        <v>0.0002212524533859959</v>
       </c>
       <c r="AO78" t="n">
-        <v>0.0002435109763645793</v>
+        <v>0.0002154410119656941</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -26277,19 +26277,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.168377359179266e-06</v>
+        <v>1.168412402280187e-06</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0006585960928301166</v>
+        <v>0.0006586158460794981</v>
       </c>
       <c r="S79" t="n">
-        <v>0.04912287353574642</v>
+        <v>0.04912434687635985</v>
       </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>0.9470009491933564</v>
+        <v>0.9470300423623846</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -26304,7 +26304,7 @@
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>9.444844669520451e-06</v>
+        <v>9.445146721500175e-06</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -26319,37 +26319,37 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>8.824376475071581e-05</v>
+        <v>8.564089299486405e-05</v>
       </c>
       <c r="AF79" t="n">
-        <v>5.867311702154178e-05</v>
+        <v>5.867487680227101e-05</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.829794458329976e-06</v>
+        <v>3.829909325220075e-06</v>
       </c>
       <c r="AH79" t="n">
-        <v>3.400041946421042e-05</v>
+        <v>3.400143923759211e-05</v>
       </c>
       <c r="AI79" t="n">
-        <v>0.001326334775630319</v>
+        <v>0.001326374556342461</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.0002672748597363188</v>
+        <v>0.0002672828761017593</v>
       </c>
       <c r="AK79" t="n">
-        <v>3.87103217758165e-05</v>
+        <v>3.871148281313208e-05</v>
       </c>
       <c r="AL79" t="n">
-        <v>2.244741427853024e-05</v>
+        <v>2.24480875430349e-05</v>
       </c>
       <c r="AM79" t="n">
-        <v>0.0009026966949900754</v>
+        <v>0.0009027237695402073</v>
       </c>
       <c r="AN79" t="n">
-        <v>0.0002212458175679937</v>
+        <v>0.0002212524533859959</v>
       </c>
       <c r="AO79" t="n">
-        <v>0.0002435109763645793</v>
+        <v>0.0002154410119656941</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -26410,19 +26410,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.168377359179266e-06</v>
+        <v>1.168412402280187e-06</v>
       </c>
       <c r="R80" t="n">
-        <v>0.0006585960928301166</v>
+        <v>0.0006586158460794981</v>
       </c>
       <c r="S80" t="n">
-        <v>0.04912287353574642</v>
+        <v>0.04912434687635985</v>
       </c>
       <c r="T80" t="n">
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>0.9470009491933564</v>
+        <v>0.9470300423623846</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -26437,7 +26437,7 @@
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>9.444844669520451e-06</v>
+        <v>9.445146721500175e-06</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -26452,37 +26452,37 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>8.824376475071581e-05</v>
+        <v>8.564089299486405e-05</v>
       </c>
       <c r="AF80" t="n">
-        <v>5.867311702154178e-05</v>
+        <v>5.867487680227101e-05</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.829794458329976e-06</v>
+        <v>3.829909325220075e-06</v>
       </c>
       <c r="AH80" t="n">
-        <v>3.400041946421042e-05</v>
+        <v>3.400143923759211e-05</v>
       </c>
       <c r="AI80" t="n">
-        <v>0.001326334775630319</v>
+        <v>0.001326374556342461</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.0002672748597363188</v>
+        <v>0.0002672828761017593</v>
       </c>
       <c r="AK80" t="n">
-        <v>3.87103217758165e-05</v>
+        <v>3.871148281313208e-05</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.244741427853024e-05</v>
+        <v>2.24480875430349e-05</v>
       </c>
       <c r="AM80" t="n">
-        <v>0.0009026966949900754</v>
+        <v>0.0009027237695402073</v>
       </c>
       <c r="AN80" t="n">
-        <v>0.0002212458175679937</v>
+        <v>0.0002212524533859959</v>
       </c>
       <c r="AO80" t="n">
-        <v>0.0002435109763645793</v>
+        <v>0.0002154410119656941</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -26682,13 +26682,13 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.008910489624372783</v>
+        <v>0.008910557611027313</v>
       </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>0.9756986138688198</v>
+        <v>0.9757060584074909</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -26703,13 +26703,13 @@
         <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.653668556767877e-05</v>
+        <v>2.653690494765252e-05</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.004455244812186392</v>
+        <v>0.004455278805513657</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -26718,13 +26718,13 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.00227357638715645</v>
+        <v>0.002271706306990686</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.007969804577894942</v>
+        <v>0.007970559097453436</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.0004121309055539275</v>
+        <v>0.0004121699229257916</v>
       </c>
       <c r="AH82" t="n">
         <v>0</v>
@@ -26748,7 +26748,7 @@
         <v>0</v>
       </c>
       <c r="AO82" t="n">
-        <v>0.0002536031384480314</v>
+        <v>0.0002471329436505694</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -26815,13 +26815,13 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.008910489624372783</v>
+        <v>0.008910557611027313</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>0.9756986138688198</v>
+        <v>0.9757060584074909</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -26836,13 +26836,13 @@
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.653668556767877e-05</v>
+        <v>2.653690494765252e-05</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.004455244812186392</v>
+        <v>0.004455278805513657</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -26851,13 +26851,13 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0.00227357638715645</v>
+        <v>0.002271706306990686</v>
       </c>
       <c r="AF83" t="n">
-        <v>0.007969804577894942</v>
+        <v>0.007970559097453436</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.0004121309055539275</v>
+        <v>0.0004121699229257916</v>
       </c>
       <c r="AH83" t="n">
         <v>0</v>
@@ -26881,7 +26881,7 @@
         <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>0.0002536031384480314</v>
+        <v>0.0002471329436505694</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -26948,13 +26948,13 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.008910489624372783</v>
+        <v>0.008910557611027313</v>
       </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0.9756986138688198</v>
+        <v>0.9757060584074909</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -26969,13 +26969,13 @@
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.653668556767877e-05</v>
+        <v>2.653690494765252e-05</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.004455244812186392</v>
+        <v>0.004455278805513657</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -26984,13 +26984,13 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.00227357638715645</v>
+        <v>0.002271706306990686</v>
       </c>
       <c r="AF84" t="n">
-        <v>0.007969804577894942</v>
+        <v>0.007970559097453436</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.0004121309055539275</v>
+        <v>0.0004121699229257916</v>
       </c>
       <c r="AH84" t="n">
         <v>0</v>
@@ -27014,7 +27014,7 @@
         <v>0</v>
       </c>
       <c r="AO84" t="n">
-        <v>0.0002536031384480314</v>
+        <v>0.0002471329436505694</v>
       </c>
       <c r="AP84" t="n">
         <v>0</v>
@@ -27214,13 +27214,13 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.000157052830560762</v>
+        <v>0.0001737951037139698</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>0.8714861567816686</v>
+        <v>0.9643890305088187</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -27235,7 +27235,7 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>8.020546620237234e-07</v>
+        <v>8.875575791718432e-07</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -27250,7 +27250,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.1282617629861237</v>
+        <v>0.03539770549849594</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -27280,7 +27280,7 @@
         <v>0</v>
       </c>
       <c r="AO86" t="n">
-        <v>9.422534698481154e-05</v>
+        <v>3.858133139218371e-05</v>
       </c>
       <c r="AP86" t="n">
         <v>0</v>
@@ -27347,13 +27347,13 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.000157052830560762</v>
+        <v>0.0001737951037139698</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>0.8714861567816686</v>
+        <v>0.9643890305088187</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>8.020546620237234e-07</v>
+        <v>8.875575791718432e-07</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -27383,7 +27383,7 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.1282617629861237</v>
+        <v>0.03539770549849594</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -27413,7 +27413,7 @@
         <v>0</v>
       </c>
       <c r="AO87" t="n">
-        <v>9.422534698481154e-05</v>
+        <v>3.858133139218371e-05</v>
       </c>
       <c r="AP87" t="n">
         <v>0</v>
@@ -27613,7 +27613,7 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.4486437806545149</v>
+        <v>0.4486437806545148</v>
       </c>
       <c r="T89" t="n">
         <v>0</v>
@@ -27740,19 +27740,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.075440141533842e-06</v>
+        <v>1.075439458721902e-06</v>
       </c>
       <c r="R90" t="n">
-        <v>0.000606208832893161</v>
+        <v>0.0006062084480027208</v>
       </c>
       <c r="S90" t="n">
-        <v>0.04521545171411233</v>
+        <v>0.04521542300619177</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>0.871672860511948</v>
+        <v>0.871672941988638</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -27782,37 +27782,37 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.07882610790953661</v>
+        <v>0.07882605786174163</v>
       </c>
       <c r="AF90" t="n">
-        <v>0.0007447422348046552</v>
+        <v>0.0007447417619574265</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.924419392036026e-05</v>
+        <v>3.924416900367436e-05</v>
       </c>
       <c r="AH90" t="n">
-        <v>3.129589565693577e-05</v>
+        <v>3.129587578673526e-05</v>
       </c>
       <c r="AI90" t="n">
-        <v>0.001220833019074512</v>
+        <v>0.001220832243950606</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.0002460147919891031</v>
+        <v>0.0002460146357908815</v>
       </c>
       <c r="AK90" t="n">
-        <v>3.563115426906969e-05</v>
+        <v>3.563113164635305e-05</v>
       </c>
       <c r="AL90" t="n">
-        <v>2.066186082699279e-05</v>
+        <v>2.066184770848927e-05</v>
       </c>
       <c r="AM90" t="n">
-        <v>0.0008308927366618954</v>
+        <v>0.0008308922091165119</v>
       </c>
       <c r="AN90" t="n">
-        <v>0.0002036470764259194</v>
+        <v>0.0002036469471275511</v>
       </c>
       <c r="AO90" t="n">
-        <v>0.0003053326277389953</v>
+        <v>0.0003053324338790528</v>
       </c>
       <c r="AP90" t="n">
         <v>0</v>
@@ -28166,10 +28166,10 @@
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>0.2151023402953605</v>
+        <v>0.2151309336461947</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.7847577379517184</v>
+        <v>0.7848689890470948</v>
       </c>
       <c r="AB93" t="n">
         <v>0</v>
@@ -28181,10 +28181,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0.0001010740873928627</v>
+        <v>9.089607914374582e-09</v>
       </c>
       <c r="AF93" t="n">
-        <v>8.870958420428733e-25</v>
+        <v>8.872210377790366e-25</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -28211,7 +28211,7 @@
         <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>3.884766552818548e-05</v>
+        <v>6.821710254137869e-08</v>
       </c>
       <c r="AP93" t="n">
         <v>0</v>
@@ -28432,10 +28432,10 @@
         <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.2151154334558294</v>
+        <v>0.2151440155969587</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.7847516419115239</v>
+        <v>0.7848559109628901</v>
       </c>
       <c r="AB95" t="n">
         <v>0</v>
@@ -28447,10 +28447,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>9.601963710860124e-05</v>
+        <v>8.63498363156754e-09</v>
       </c>
       <c r="AF95" t="n">
-        <v>8.427345032590673e-25</v>
+        <v>8.428459412881953e-25</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -28477,7 +28477,7 @@
         <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>3.690499553808229e-05</v>
+        <v>6.480516753559219e-08</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -28565,10 +28565,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>0.1949549526794055</v>
+        <v>0.1949720456720377</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.7121208083064552</v>
+        <v>0.7121832446568139</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>
@@ -28580,13 +28580,13 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0.0919485730550062</v>
+        <v>0.09187224180078066</v>
       </c>
       <c r="AF96" t="n">
-        <v>0.0008057923219606559</v>
+        <v>0.0008058624594596834</v>
       </c>
       <c r="AG96" t="n">
-        <v>4.166876566323062e-05</v>
+        <v>4.167239258164562e-05</v>
       </c>
       <c r="AH96" t="n">
         <v>0</v>
@@ -28610,7 +28610,7 @@
         <v>0</v>
       </c>
       <c r="AO96" t="n">
-        <v>0.0001282048715090819</v>
+        <v>0.0001249330183263743</v>
       </c>
       <c r="AP96" t="n">
         <v>0</v>
@@ -28683,7 +28683,7 @@
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>0.9864864864864864</v>
+        <v>0.9864864864864865</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
